--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY179"/>
+  <dimension ref="A1:AY184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2085,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121501589</v>
+        <v>121499942</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>79688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,39 +2101,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510074</v>
+        <v>509886</v>
       </c>
       <c r="R15" t="n">
-        <v>7063202</v>
+        <v>7062840</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121499942</v>
+        <v>121501589</v>
       </c>
       <c r="B16" t="n">
-        <v>79688</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,34 +2203,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509886</v>
+        <v>510074</v>
       </c>
       <c r="R16" t="n">
-        <v>7062840</v>
+        <v>7063202</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3187,10 +3187,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121499616</v>
+        <v>121499946</v>
       </c>
       <c r="B25" t="n">
-        <v>57370</v>
+        <v>79689</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3203,39 +3203,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509751</v>
+        <v>509886</v>
       </c>
       <c r="R25" t="n">
-        <v>7062897</v>
+        <v>7062832</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3294,10 +3289,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121499954</v>
+        <v>121499616</v>
       </c>
       <c r="B26" t="n">
-        <v>57354</v>
+        <v>57370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3310,16 +3305,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3339,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509886</v>
+        <v>509751</v>
       </c>
       <c r="R26" t="n">
-        <v>7062840</v>
+        <v>7062897</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,10 +3396,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121499946</v>
+        <v>121499954</v>
       </c>
       <c r="B27" t="n">
-        <v>79689</v>
+        <v>57354</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3417,24 +3412,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
@@ -3444,7 +3444,7 @@
         <v>509886</v>
       </c>
       <c r="R27" t="n">
-        <v>7062832</v>
+        <v>7062840</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121500431</v>
+        <v>121499642</v>
       </c>
       <c r="B41" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4948,48 +4948,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509890</v>
+        <v>509800</v>
       </c>
       <c r="R41" t="n">
-        <v>7062735</v>
+        <v>7062887</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5032,31 +5018,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5073,10 +5034,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121499642</v>
+        <v>121500431</v>
       </c>
       <c r="B42" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5089,34 +5050,48 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509800</v>
+        <v>509890</v>
       </c>
       <c r="R42" t="n">
-        <v>7062887</v>
+        <v>7062735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5159,6 +5134,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5175,10 +5175,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121501875</v>
+        <v>121502557</v>
       </c>
       <c r="B43" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5191,34 +5191,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510108</v>
+        <v>509798</v>
       </c>
       <c r="R43" t="n">
-        <v>7063267</v>
+        <v>7063019</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5277,10 +5282,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121502557</v>
+        <v>121501875</v>
       </c>
       <c r="B44" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5293,39 +5298,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509798</v>
+        <v>510108</v>
       </c>
       <c r="R44" t="n">
-        <v>7063019</v>
+        <v>7063267</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121499643</v>
+        <v>121499875</v>
       </c>
       <c r="B45" t="n">
-        <v>78607</v>
+        <v>91396</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5396,25 +5396,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>509815</v>
+        <v>509861</v>
       </c>
       <c r="R45" t="n">
-        <v>7062883</v>
+        <v>7062861</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5486,10 +5486,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121499500</v>
+        <v>121499643</v>
       </c>
       <c r="B46" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5502,39 +5502,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509741</v>
+        <v>509815</v>
       </c>
       <c r="R46" t="n">
-        <v>7062887</v>
+        <v>7062883</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5593,10 +5588,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121499875</v>
+        <v>121499500</v>
       </c>
       <c r="B47" t="n">
-        <v>91396</v>
+        <v>57354</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5605,38 +5600,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509861</v>
+        <v>509741</v>
       </c>
       <c r="R47" t="n">
-        <v>7062861</v>
+        <v>7062887</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -7650,10 +7650,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121499686</v>
+        <v>121500024</v>
       </c>
       <c r="B66" t="n">
-        <v>57354</v>
+        <v>90709</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7666,32 +7666,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7700,10 +7699,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509801</v>
+        <v>509829</v>
       </c>
       <c r="R66" t="n">
-        <v>7062864</v>
+        <v>7062852</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7764,12 +7763,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7787,10 +7786,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121500024</v>
+        <v>121499686</v>
       </c>
       <c r="B67" t="n">
-        <v>90709</v>
+        <v>57354</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7803,31 +7802,32 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509829</v>
+        <v>509801</v>
       </c>
       <c r="R67" t="n">
-        <v>7062852</v>
+        <v>7062864</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7923,10 +7923,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121502591</v>
+        <v>121499654</v>
       </c>
       <c r="B68" t="n">
-        <v>56558</v>
+        <v>78607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7939,21 +7939,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509769</v>
+        <v>509801</v>
       </c>
       <c r="R68" t="n">
-        <v>7063041</v>
+        <v>7062864</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8009,6 +8009,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8025,7 +8050,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121502801</v>
+        <v>121499578</v>
       </c>
       <c r="B69" t="n">
         <v>57354</v>
@@ -8061,7 +8086,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8070,10 +8095,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>509714</v>
+        <v>509760</v>
       </c>
       <c r="R69" t="n">
-        <v>7063026</v>
+        <v>7062882</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8132,10 +8157,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121501256</v>
+        <v>121502591</v>
       </c>
       <c r="B70" t="n">
-        <v>57354</v>
+        <v>56558</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8148,16 +8173,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8166,21 +8191,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>509991</v>
+        <v>509769</v>
       </c>
       <c r="R70" t="n">
-        <v>7062974</v>
+        <v>7063041</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8239,7 +8259,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121499578</v>
+        <v>121502801</v>
       </c>
       <c r="B71" t="n">
         <v>57354</v>
@@ -8275,7 +8295,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8284,10 +8304,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509760</v>
+        <v>509714</v>
       </c>
       <c r="R71" t="n">
-        <v>7062882</v>
+        <v>7063026</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8346,10 +8366,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121499654</v>
+        <v>121501256</v>
       </c>
       <c r="B72" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8362,34 +8382,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509801</v>
+        <v>509991</v>
       </c>
       <c r="R72" t="n">
-        <v>7062864</v>
+        <v>7062974</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8432,31 +8457,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -11023,10 +11023,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121513668</v>
+        <v>121511869</v>
       </c>
       <c r="B96" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11039,39 +11039,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>509824</v>
+        <v>509783</v>
       </c>
       <c r="R96" t="n">
-        <v>7063064</v>
+        <v>7063234</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11114,31 +11109,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11155,10 +11125,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121513063</v>
+        <v>121513668</v>
       </c>
       <c r="B97" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11171,27 +11141,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11200,10 +11170,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>509741</v>
+        <v>509824</v>
       </c>
       <c r="R97" t="n">
-        <v>7063089</v>
+        <v>7063064</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11246,6 +11216,31 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11262,10 +11257,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121511869</v>
+        <v>121513063</v>
       </c>
       <c r="B98" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11278,34 +11273,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>509783</v>
+        <v>509741</v>
       </c>
       <c r="R98" t="n">
-        <v>7063234</v>
+        <v>7063089</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12537,7 +12537,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121511810</v>
+        <v>121510881</v>
       </c>
       <c r="B109" t="n">
         <v>57354</v>
@@ -12582,10 +12582,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>509809</v>
+        <v>509857</v>
       </c>
       <c r="R109" t="n">
-        <v>7063240</v>
+        <v>7063220</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12771,10 +12771,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121510881</v>
+        <v>121513877</v>
       </c>
       <c r="B111" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12787,39 +12787,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>509857</v>
+        <v>509777</v>
       </c>
       <c r="R111" t="n">
-        <v>7063220</v>
+        <v>7062985</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12862,6 +12862,31 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -12878,10 +12903,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121513877</v>
+        <v>121513661</v>
       </c>
       <c r="B112" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12894,27 +12919,27 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12923,13 +12948,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>509777</v>
+        <v>509799</v>
       </c>
       <c r="R112" t="n">
-        <v>7062985</v>
+        <v>7063072</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12969,31 +12994,6 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -13010,10 +13010,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121513661</v>
+        <v>121509655</v>
       </c>
       <c r="B113" t="n">
-        <v>57354</v>
+        <v>57507</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13026,42 +13026,51 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>509799</v>
+        <v>509663</v>
       </c>
       <c r="R113" t="n">
-        <v>7063072</v>
+        <v>7063347</v>
       </c>
       <c r="S113" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13101,6 +13110,11 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -13117,7 +13131,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121509655</v>
+        <v>121509418</v>
       </c>
       <c r="B114" t="n">
         <v>57507</v>
@@ -13157,12 +13171,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13171,10 +13180,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>509663</v>
+        <v>509603</v>
       </c>
       <c r="R114" t="n">
-        <v>7063347</v>
+        <v>7063266</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13217,11 +13226,6 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13238,10 +13242,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121509418</v>
+        <v>121511810</v>
       </c>
       <c r="B115" t="n">
-        <v>57507</v>
+        <v>57354</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13254,31 +13258,27 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>509603</v>
+        <v>509809</v>
       </c>
       <c r="R115" t="n">
-        <v>7063266</v>
+        <v>7063240</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -18452,10 +18452,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121513205</v>
+        <v>121510620</v>
       </c>
       <c r="B162" t="n">
-        <v>57354</v>
+        <v>79723</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18464,43 +18464,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>509802</v>
+        <v>509826</v>
       </c>
       <c r="R162" t="n">
-        <v>7063094</v>
+        <v>7063254</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18559,10 +18554,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121510620</v>
+        <v>121509893</v>
       </c>
       <c r="B163" t="n">
-        <v>79723</v>
+        <v>57354</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18571,38 +18566,43 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>509826</v>
+        <v>509672</v>
       </c>
       <c r="R163" t="n">
-        <v>7063254</v>
+        <v>7063416</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18661,7 +18661,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121509893</v>
+        <v>121513205</v>
       </c>
       <c r="B164" t="n">
         <v>57354</v>
@@ -18702,14 +18702,14 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>509672</v>
+        <v>509802</v>
       </c>
       <c r="R164" t="n">
-        <v>7063416</v>
+        <v>7063094</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19976,10 +19976,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121513768</v>
+        <v>121536426</v>
       </c>
       <c r="B174" t="n">
-        <v>90660</v>
+        <v>90713</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19992,37 +19992,41 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>509770</v>
+        <v>510009</v>
       </c>
       <c r="R174" t="n">
-        <v>7063048</v>
+        <v>7063068</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20049,12 +20053,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20084,12 +20088,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -20107,10 +20111,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121536426</v>
+        <v>121513768</v>
       </c>
       <c r="B175" t="n">
-        <v>90713</v>
+        <v>90660</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20123,41 +20127,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>510009</v>
+        <v>509770</v>
       </c>
       <c r="R175" t="n">
-        <v>7063068</v>
+        <v>7063048</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20184,12 +20184,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20219,12 +20219,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -20766,6 +20766,629 @@
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>121540413</v>
+      </c>
+      <c r="B180" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Sörpkaret, Nyland, Gåxsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>510014</v>
+      </c>
+      <c r="R180" t="n">
+        <v>7063010</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>121541649</v>
+      </c>
+      <c r="B181" t="n">
+        <v>82392</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Sörpkaret, Jmt</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>510075</v>
+      </c>
+      <c r="R181" t="n">
+        <v>7063176</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>121541339</v>
+      </c>
+      <c r="B182" t="n">
+        <v>79593</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Sörpkaret, Jmt</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>510072</v>
+      </c>
+      <c r="R182" t="n">
+        <v>7063162</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>På en grov asp med brösthöjdsdiameter på 84,5 cm.</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>121541263</v>
+      </c>
+      <c r="B183" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Sörpkaret, Jmt</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>509813</v>
+      </c>
+      <c r="R183" t="n">
+        <v>7063049</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>121502652</v>
+      </c>
+      <c r="B184" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>510074</v>
+      </c>
+      <c r="R184" t="n">
+        <v>7063170</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -2085,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121499942</v>
+        <v>121501589</v>
       </c>
       <c r="B15" t="n">
-        <v>79688</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,34 +2101,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509886</v>
+        <v>510074</v>
       </c>
       <c r="R15" t="n">
-        <v>7062840</v>
+        <v>7063202</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121501589</v>
+        <v>121499942</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>79688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,39 +2208,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510074</v>
+        <v>509886</v>
       </c>
       <c r="R16" t="n">
-        <v>7063202</v>
+        <v>7062840</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121502932</v>
+        <v>121499979</v>
       </c>
       <c r="B17" t="n">
-        <v>56558</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,44 +2310,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509772</v>
+        <v>509829</v>
       </c>
       <c r="R17" t="n">
-        <v>7063098</v>
+        <v>7062852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,6 +2384,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2411,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121502120</v>
+        <v>121502932</v>
       </c>
       <c r="B18" t="n">
-        <v>57465</v>
+        <v>56558</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,20 +2433,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2444,19 +2454,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2465,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510010</v>
+        <v>509772</v>
       </c>
       <c r="R18" t="n">
-        <v>7063185</v>
+        <v>7063098</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,6 +2517,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2527,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121500038</v>
+        <v>121502120</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>57465</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2539,38 +2550,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509829</v>
+        <v>510010</v>
       </c>
       <c r="R19" t="n">
-        <v>7062852</v>
+        <v>7063185</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,31 +2638,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121501454</v>
+        <v>121501367</v>
       </c>
       <c r="B28" t="n">
-        <v>56558</v>
+        <v>90731</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3519,48 +3519,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509999</v>
+        <v>510023</v>
       </c>
       <c r="R28" t="n">
-        <v>7063087</v>
+        <v>7063038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3603,11 +3589,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3624,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121502766</v>
+        <v>121502443</v>
       </c>
       <c r="B29" t="n">
-        <v>57354</v>
+        <v>90709</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3640,39 +3621,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509728</v>
+        <v>509834</v>
       </c>
       <c r="R29" t="n">
-        <v>7063047</v>
+        <v>7063042</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3731,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121500197</v>
+        <v>121500392</v>
       </c>
       <c r="B30" t="n">
-        <v>57354</v>
+        <v>74704</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3743,43 +3719,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509923</v>
+        <v>509922</v>
       </c>
       <c r="R30" t="n">
-        <v>7062805</v>
+        <v>7062815</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3838,10 +3809,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121501367</v>
+        <v>121500154</v>
       </c>
       <c r="B31" t="n">
-        <v>90731</v>
+        <v>79689</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3854,21 +3825,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3878,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510023</v>
+        <v>509884</v>
       </c>
       <c r="R31" t="n">
-        <v>7063038</v>
+        <v>7062810</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,10 +3911,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121502443</v>
+        <v>121501454</v>
       </c>
       <c r="B32" t="n">
-        <v>90709</v>
+        <v>56558</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,34 +3927,48 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509834</v>
+        <v>509999</v>
       </c>
       <c r="R32" t="n">
-        <v>7063042</v>
+        <v>7063087</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4026,6 +4011,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4042,10 +4032,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121500392</v>
+        <v>121502766</v>
       </c>
       <c r="B33" t="n">
-        <v>74704</v>
+        <v>57354</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4054,38 +4044,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509922</v>
+        <v>509728</v>
       </c>
       <c r="R33" t="n">
-        <v>7062815</v>
+        <v>7063047</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4144,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121500154</v>
+        <v>121500197</v>
       </c>
       <c r="B34" t="n">
-        <v>79689</v>
+        <v>57354</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,34 +4155,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509884</v>
+        <v>509923</v>
       </c>
       <c r="R34" t="n">
-        <v>7062810</v>
+        <v>7062805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121500134</v>
+        <v>121502031</v>
       </c>
       <c r="B38" t="n">
-        <v>57354</v>
+        <v>74713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4577,44 +4577,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509829</v>
+        <v>510054</v>
       </c>
       <c r="R38" t="n">
-        <v>7062852</v>
+        <v>7063204</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4657,31 +4647,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4698,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121502031</v>
+        <v>121500555</v>
       </c>
       <c r="B39" t="n">
-        <v>74713</v>
+        <v>90731</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4714,34 +4679,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>510054</v>
+        <v>509882</v>
       </c>
       <c r="R39" t="n">
-        <v>7063204</v>
+        <v>7062734</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4784,6 +4754,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4800,10 +4795,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121500555</v>
+        <v>121500134</v>
       </c>
       <c r="B40" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4816,27 +4811,32 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509882</v>
+        <v>509829</v>
       </c>
       <c r="R40" t="n">
-        <v>7062734</v>
+        <v>7062852</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,12 +4909,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121499642</v>
+        <v>121500431</v>
       </c>
       <c r="B41" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4948,34 +4948,48 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509800</v>
+        <v>509890</v>
       </c>
       <c r="R41" t="n">
-        <v>7062887</v>
+        <v>7062735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5018,6 +5032,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5034,10 +5073,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121500431</v>
+        <v>121499642</v>
       </c>
       <c r="B42" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5050,48 +5089,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509890</v>
+        <v>509800</v>
       </c>
       <c r="R42" t="n">
-        <v>7062735</v>
+        <v>7062887</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5134,31 +5159,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -6760,10 +6760,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121500710</v>
+        <v>121499843</v>
       </c>
       <c r="B58" t="n">
-        <v>57507</v>
+        <v>90713</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6776,43 +6776,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>509996</v>
+        <v>509857</v>
       </c>
       <c r="R58" t="n">
-        <v>7063006</v>
+        <v>7062855</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6871,10 +6862,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121499843</v>
+        <v>121500710</v>
       </c>
       <c r="B59" t="n">
-        <v>90713</v>
+        <v>57507</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6887,34 +6878,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>509857</v>
+        <v>509996</v>
       </c>
       <c r="R59" t="n">
-        <v>7062855</v>
+        <v>7063006</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7923,10 +7923,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121499654</v>
+        <v>121502591</v>
       </c>
       <c r="B68" t="n">
-        <v>78607</v>
+        <v>56558</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7939,21 +7939,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509801</v>
+        <v>509769</v>
       </c>
       <c r="R68" t="n">
-        <v>7062864</v>
+        <v>7063041</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8009,31 +8009,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8050,7 +8025,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121499578</v>
+        <v>121502801</v>
       </c>
       <c r="B69" t="n">
         <v>57354</v>
@@ -8086,7 +8061,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8095,10 +8070,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>509760</v>
+        <v>509714</v>
       </c>
       <c r="R69" t="n">
-        <v>7062882</v>
+        <v>7063026</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8157,10 +8132,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121502591</v>
+        <v>121501256</v>
       </c>
       <c r="B70" t="n">
-        <v>56558</v>
+        <v>57354</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8173,16 +8148,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8191,16 +8166,21 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>509769</v>
+        <v>509991</v>
       </c>
       <c r="R70" t="n">
-        <v>7063041</v>
+        <v>7062974</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8259,7 +8239,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121502801</v>
+        <v>121499578</v>
       </c>
       <c r="B71" t="n">
         <v>57354</v>
@@ -8295,7 +8275,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8304,10 +8284,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509714</v>
+        <v>509760</v>
       </c>
       <c r="R71" t="n">
-        <v>7063026</v>
+        <v>7062882</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8366,10 +8346,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121501256</v>
+        <v>121499654</v>
       </c>
       <c r="B72" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8382,39 +8362,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509991</v>
+        <v>509801</v>
       </c>
       <c r="R72" t="n">
-        <v>7062974</v>
+        <v>7062864</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8457,6 +8432,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -11023,10 +11023,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121511869</v>
+        <v>121513668</v>
       </c>
       <c r="B96" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11039,34 +11039,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>509783</v>
+        <v>509824</v>
       </c>
       <c r="R96" t="n">
-        <v>7063234</v>
+        <v>7063064</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11109,6 +11114,31 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11125,10 +11155,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121513668</v>
+        <v>121513063</v>
       </c>
       <c r="B97" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11141,27 +11171,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11170,10 +11200,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>509824</v>
+        <v>509741</v>
       </c>
       <c r="R97" t="n">
-        <v>7063064</v>
+        <v>7063089</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11216,31 +11246,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11257,10 +11262,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121513063</v>
+        <v>121511869</v>
       </c>
       <c r="B98" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11273,39 +11278,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>509741</v>
+        <v>509783</v>
       </c>
       <c r="R98" t="n">
-        <v>7063089</v>
+        <v>7063234</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -19976,10 +19976,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121536426</v>
+        <v>121513768</v>
       </c>
       <c r="B174" t="n">
-        <v>90713</v>
+        <v>90660</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19992,41 +19992,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>510009</v>
+        <v>509770</v>
       </c>
       <c r="R174" t="n">
-        <v>7063068</v>
+        <v>7063048</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20053,12 +20049,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20088,12 +20084,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -20111,10 +20107,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121513768</v>
+        <v>121536426</v>
       </c>
       <c r="B175" t="n">
-        <v>90660</v>
+        <v>90713</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20127,37 +20123,41 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>509770</v>
+        <v>510009</v>
       </c>
       <c r="R175" t="n">
-        <v>7063048</v>
+        <v>7063068</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20184,12 +20184,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20219,12 +20219,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -20768,10 +20768,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121540413</v>
+        <v>121541649</v>
       </c>
       <c r="B180" t="n">
-        <v>57355</v>
+        <v>82392</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20784,42 +20784,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Sörpkaret, Nyland, Gåxsjö, Jmt</t>
+          <t>Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>510014</v>
+        <v>510075</v>
       </c>
       <c r="R180" t="n">
-        <v>7063010</v>
+        <v>7063176</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20860,6 +20855,7 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -20878,10 +20874,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121541649</v>
+        <v>121540413</v>
       </c>
       <c r="B181" t="n">
-        <v>82392</v>
+        <v>57355</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20894,37 +20890,42 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Nyland, Gåxsjö, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>510075</v>
+        <v>510014</v>
       </c>
       <c r="R181" t="n">
-        <v>7063176</v>
+        <v>7063010</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20965,7 +20966,6 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -6825,10 +6825,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121502031</v>
+        <v>121501454</v>
       </c>
       <c r="B58" t="n">
-        <v>74714</v>
+        <v>56559</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6841,34 +6841,48 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>510054</v>
+        <v>509999</v>
       </c>
       <c r="R58" t="n">
-        <v>7063204</v>
+        <v>7063087</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6911,6 +6925,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -6927,10 +6946,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121501454</v>
+        <v>121502031</v>
       </c>
       <c r="B59" t="n">
-        <v>56559</v>
+        <v>74714</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6943,48 +6962,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>509999</v>
+        <v>510054</v>
       </c>
       <c r="R59" t="n">
-        <v>7063087</v>
+        <v>7063204</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7027,11 +7032,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7486,10 +7486,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121501666</v>
+        <v>121501394</v>
       </c>
       <c r="B64" t="n">
-        <v>90737</v>
+        <v>57355</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7502,27 +7502,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>509999</v>
+        <v>510035</v>
       </c>
       <c r="R64" t="n">
-        <v>7063087</v>
+        <v>7063074</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7577,31 +7577,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7618,10 +7593,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121499492</v>
+        <v>121499843</v>
       </c>
       <c r="B65" t="n">
-        <v>57355</v>
+        <v>90719</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7634,39 +7609,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>509751</v>
+        <v>509857</v>
       </c>
       <c r="R65" t="n">
-        <v>7062898</v>
+        <v>7062855</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7725,10 +7695,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121499843</v>
+        <v>121501666</v>
       </c>
       <c r="B66" t="n">
-        <v>90719</v>
+        <v>90737</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7741,34 +7711,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509857</v>
+        <v>509999</v>
       </c>
       <c r="R66" t="n">
-        <v>7062855</v>
+        <v>7063087</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7811,6 +7786,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7827,10 +7827,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121503055</v>
+        <v>121499492</v>
       </c>
       <c r="B67" t="n">
-        <v>78608</v>
+        <v>57355</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7843,39 +7843,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Östra Nyland, Östra Nyland, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509562</v>
+        <v>509751</v>
       </c>
       <c r="R67" t="n">
-        <v>7063187</v>
+        <v>7062898</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121501394</v>
+        <v>121503055</v>
       </c>
       <c r="B68" t="n">
-        <v>57355</v>
+        <v>78608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7950,39 +7950,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Östra Nyland, Östra Nyland, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>510035</v>
+        <v>509562</v>
       </c>
       <c r="R68" t="n">
-        <v>7063074</v>
+        <v>7063187</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -10245,10 +10245,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121509983</v>
+        <v>121510661</v>
       </c>
       <c r="B89" t="n">
-        <v>82392</v>
+        <v>90737</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10261,21 +10261,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10285,10 +10285,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>509716</v>
+        <v>509840</v>
       </c>
       <c r="R89" t="n">
-        <v>7063402</v>
+        <v>7063229</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10347,10 +10347,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121510201</v>
+        <v>121512968</v>
       </c>
       <c r="B90" t="n">
-        <v>90719</v>
+        <v>90737</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10363,34 +10363,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>509782</v>
+        <v>509750</v>
       </c>
       <c r="R90" t="n">
-        <v>7063393</v>
+        <v>7063102</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10449,7 +10449,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121510661</v>
+        <v>121512342</v>
       </c>
       <c r="B91" t="n">
         <v>90737</v>
@@ -10483,16 +10483,21 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>509840</v>
+        <v>509781</v>
       </c>
       <c r="R91" t="n">
-        <v>7063229</v>
+        <v>7063131</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10535,6 +10540,31 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10551,10 +10581,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121512968</v>
+        <v>121513877</v>
       </c>
       <c r="B92" t="n">
-        <v>90737</v>
+        <v>78608</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10567,34 +10597,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>509750</v>
+        <v>509777</v>
       </c>
       <c r="R92" t="n">
-        <v>7063102</v>
+        <v>7062985</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10637,6 +10672,31 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10653,10 +10713,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121512342</v>
+        <v>121510429</v>
       </c>
       <c r="B93" t="n">
-        <v>90737</v>
+        <v>78608</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10669,39 +10729,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>509781</v>
+        <v>509795</v>
       </c>
       <c r="R93" t="n">
-        <v>7063131</v>
+        <v>7063275</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10762,12 +10817,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11213,10 +11268,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121513877</v>
+        <v>121509983</v>
       </c>
       <c r="B98" t="n">
-        <v>78608</v>
+        <v>82392</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11229,39 +11284,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>509777</v>
+        <v>509716</v>
       </c>
       <c r="R98" t="n">
-        <v>7062985</v>
+        <v>7063402</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11304,31 +11354,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11345,10 +11370,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121510429</v>
+        <v>121510201</v>
       </c>
       <c r="B99" t="n">
-        <v>78608</v>
+        <v>90719</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11361,21 +11386,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11385,10 +11410,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>509795</v>
+        <v>509782</v>
       </c>
       <c r="R99" t="n">
-        <v>7063275</v>
+        <v>7063393</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11431,31 +11456,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13103,10 +13103,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121509451</v>
+        <v>121512639</v>
       </c>
       <c r="B114" t="n">
-        <v>79689</v>
+        <v>82392</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13119,34 +13119,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>509661</v>
+        <v>509713</v>
       </c>
       <c r="R114" t="n">
-        <v>7063260</v>
+        <v>7063158</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13205,10 +13205,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121509587</v>
+        <v>121509451</v>
       </c>
       <c r="B115" t="n">
-        <v>57371</v>
+        <v>79689</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13221,43 +13221,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>509623</v>
+        <v>509661</v>
       </c>
       <c r="R115" t="n">
-        <v>7063364</v>
+        <v>7063260</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13316,7 +13307,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121509381</v>
+        <v>121509587</v>
       </c>
       <c r="B116" t="n">
         <v>57371</v>
@@ -13349,10 +13340,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13361,10 +13356,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>509555</v>
+        <v>509623</v>
       </c>
       <c r="R116" t="n">
-        <v>7063261</v>
+        <v>7063364</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13423,10 +13418,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121512639</v>
+        <v>121509381</v>
       </c>
       <c r="B117" t="n">
-        <v>82392</v>
+        <v>57371</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13439,34 +13434,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>509713</v>
+        <v>509555</v>
       </c>
       <c r="R117" t="n">
-        <v>7063158</v>
+        <v>7063261</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15899,10 +15899,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121510127</v>
+        <v>121510603</v>
       </c>
       <c r="B139" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15915,21 +15915,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15939,10 +15939,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>509663</v>
+        <v>509826</v>
       </c>
       <c r="R139" t="n">
-        <v>7063347</v>
+        <v>7063254</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15985,31 +15985,6 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -16026,10 +16001,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121510603</v>
+        <v>121510127</v>
       </c>
       <c r="B140" t="n">
-        <v>79690</v>
+        <v>78608</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16042,21 +16017,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16066,10 +16041,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>509826</v>
+        <v>509663</v>
       </c>
       <c r="R140" t="n">
-        <v>7063254</v>
+        <v>7063347</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16112,6 +16087,31 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -16877,10 +16877,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121509895</v>
+        <v>121509418</v>
       </c>
       <c r="B148" t="n">
-        <v>57355</v>
+        <v>57508</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16893,27 +16893,31 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16922,10 +16926,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>509672</v>
+        <v>509603</v>
       </c>
       <c r="R148" t="n">
-        <v>7063419</v>
+        <v>7063266</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16984,7 +16988,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121513661</v>
+        <v>121509895</v>
       </c>
       <c r="B149" t="n">
         <v>57355</v>
@@ -17025,17 +17029,17 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>509799</v>
+        <v>509672</v>
       </c>
       <c r="R149" t="n">
-        <v>7063072</v>
+        <v>7063419</v>
       </c>
       <c r="S149" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17091,7 +17095,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121512903</v>
+        <v>121513661</v>
       </c>
       <c r="B150" t="n">
         <v>57355</v>
@@ -17136,13 +17140,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>509758</v>
+        <v>509799</v>
       </c>
       <c r="R150" t="n">
-        <v>7063118</v>
+        <v>7063072</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17198,10 +17202,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121514198</v>
+        <v>121512903</v>
       </c>
       <c r="B151" t="n">
-        <v>56559</v>
+        <v>57355</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17214,16 +17218,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -17231,19 +17235,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17252,10 +17247,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>509877</v>
+        <v>509758</v>
       </c>
       <c r="R151" t="n">
-        <v>7062713</v>
+        <v>7063118</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17314,10 +17309,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121509418</v>
+        <v>121514198</v>
       </c>
       <c r="B152" t="n">
-        <v>57508</v>
+        <v>56559</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17330,26 +17325,31 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -17359,14 +17359,14 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>509603</v>
+        <v>509877</v>
       </c>
       <c r="R152" t="n">
-        <v>7063266</v>
+        <v>7062713</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -19034,10 +19034,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121537514</v>
+        <v>121501176</v>
       </c>
       <c r="B167" t="n">
-        <v>91063</v>
+        <v>90719</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19046,30 +19046,34 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -19132,22 +19136,22 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Phellinidium ferrugineofuscum</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -19305,10 +19309,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121501176</v>
+        <v>121537514</v>
       </c>
       <c r="B169" t="n">
-        <v>90719</v>
+        <v>91063</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19317,34 +19321,30 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -19407,22 +19407,22 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121499735</v>
+        <v>121499830</v>
       </c>
       <c r="B2" t="n">
-        <v>82393</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509823</v>
+        <v>509856</v>
       </c>
       <c r="R2" t="n">
         <v>7062863</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121499830</v>
+        <v>121499735</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>82393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509856</v>
+        <v>509823</v>
       </c>
       <c r="R3" t="n">
         <v>7062863</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121499884</v>
+        <v>121499476</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2329,34 +2329,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509829</v>
+        <v>509728</v>
       </c>
       <c r="R17" t="n">
-        <v>7062852</v>
+        <v>7062896</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,11 +2396,6 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2404,31 +2404,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2445,10 +2420,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121499476</v>
+        <v>121499884</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,39 +2436,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509728</v>
+        <v>509829</v>
       </c>
       <c r="R18" t="n">
-        <v>7062896</v>
+        <v>7062852</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2528,6 +2498,11 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2536,6 +2511,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121499839</v>
+        <v>121499605</v>
       </c>
       <c r="B20" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,34 +2675,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509822</v>
+        <v>509785</v>
       </c>
       <c r="R20" t="n">
-        <v>7062861</v>
+        <v>7062874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,31 +2750,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2786,10 +2766,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121499605</v>
+        <v>121499839</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2802,39 +2782,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509785</v>
+        <v>509822</v>
       </c>
       <c r="R21" t="n">
-        <v>7062874</v>
+        <v>7062861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2877,6 +2852,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2893,10 +2893,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121501985</v>
+        <v>121500282</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,39 +2909,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510064</v>
+        <v>509915</v>
       </c>
       <c r="R22" t="n">
-        <v>7063220</v>
+        <v>7062758</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121500282</v>
+        <v>121501985</v>
       </c>
       <c r="B23" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,43 +3020,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509915</v>
+        <v>510064</v>
       </c>
       <c r="R23" t="n">
-        <v>7062758</v>
+        <v>7063220</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -5016,10 +5016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121502766</v>
+        <v>121500126</v>
       </c>
       <c r="B41" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5028,43 +5028,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509728</v>
+        <v>509872</v>
       </c>
       <c r="R41" t="n">
-        <v>7063047</v>
+        <v>7062810</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5123,10 +5118,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121501377</v>
+        <v>121502766</v>
       </c>
       <c r="B42" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5139,34 +5134,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510023</v>
+        <v>509728</v>
       </c>
       <c r="R42" t="n">
-        <v>7063038</v>
+        <v>7063047</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5225,10 +5225,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121500126</v>
+        <v>121502591</v>
       </c>
       <c r="B43" t="n">
-        <v>79719</v>
+        <v>56560</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5237,25 +5237,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509872</v>
+        <v>509769</v>
       </c>
       <c r="R43" t="n">
-        <v>7062810</v>
+        <v>7063041</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5327,10 +5327,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121502591</v>
+        <v>121501377</v>
       </c>
       <c r="B44" t="n">
-        <v>56560</v>
+        <v>90720</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509769</v>
+        <v>510023</v>
       </c>
       <c r="R44" t="n">
-        <v>7063041</v>
+        <v>7063038</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121499643</v>
+        <v>121501890</v>
       </c>
       <c r="B48" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5765,34 +5765,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>509815</v>
+        <v>510108</v>
       </c>
       <c r="R48" t="n">
-        <v>7062883</v>
+        <v>7063268</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5953,10 +5958,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121501890</v>
+        <v>121499643</v>
       </c>
       <c r="B50" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5969,39 +5974,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>510108</v>
+        <v>509815</v>
       </c>
       <c r="R50" t="n">
-        <v>7063268</v>
+        <v>7062883</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121499875</v>
+        <v>121502684</v>
       </c>
       <c r="B51" t="n">
-        <v>91403</v>
+        <v>90738</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6072,25 +6072,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509861</v>
+        <v>509752</v>
       </c>
       <c r="R51" t="n">
-        <v>7062861</v>
+        <v>7063039</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121499799</v>
+        <v>121500555</v>
       </c>
       <c r="B52" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6178,27 +6178,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>509823</v>
+        <v>509882</v>
       </c>
       <c r="R52" t="n">
-        <v>7062878</v>
+        <v>7062734</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6253,6 +6253,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6269,7 +6294,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121499492</v>
+        <v>121502557</v>
       </c>
       <c r="B53" t="n">
         <v>57356</v>
@@ -6314,10 +6339,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>509751</v>
+        <v>509798</v>
       </c>
       <c r="R53" t="n">
-        <v>7062898</v>
+        <v>7063019</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6376,10 +6401,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121502684</v>
+        <v>121499875</v>
       </c>
       <c r="B54" t="n">
-        <v>90738</v>
+        <v>91403</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6388,25 +6413,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6416,10 +6441,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>509752</v>
+        <v>509861</v>
       </c>
       <c r="R54" t="n">
-        <v>7063039</v>
+        <v>7062861</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6478,10 +6503,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121500555</v>
+        <v>121499799</v>
       </c>
       <c r="B55" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6494,27 +6519,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6523,10 +6548,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>509882</v>
+        <v>509823</v>
       </c>
       <c r="R55" t="n">
-        <v>7062734</v>
+        <v>7062878</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6569,31 +6594,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6610,7 +6610,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121502557</v>
+        <v>121499492</v>
       </c>
       <c r="B56" t="n">
         <v>57356</v>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>509798</v>
+        <v>509751</v>
       </c>
       <c r="R56" t="n">
-        <v>7063019</v>
+        <v>7062898</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7058,10 +7058,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121502942</v>
+        <v>121503091</v>
       </c>
       <c r="B60" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7074,34 +7074,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Östra Nyland, Östra Nyland, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>509621</v>
+        <v>509565</v>
       </c>
       <c r="R60" t="n">
-        <v>7063163</v>
+        <v>7063172</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7160,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121503226</v>
+        <v>121502942</v>
       </c>
       <c r="B61" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7176,34 +7181,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>509545</v>
+        <v>509621</v>
       </c>
       <c r="R61" t="n">
-        <v>7063237</v>
+        <v>7063163</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7262,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121503091</v>
+        <v>121503226</v>
       </c>
       <c r="B62" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7278,39 +7283,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Östra Nyland, Östra Nyland, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>509565</v>
+        <v>509545</v>
       </c>
       <c r="R62" t="n">
-        <v>7063172</v>
+        <v>7063237</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8123,10 +8123,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121502170</v>
+        <v>121499654</v>
       </c>
       <c r="B70" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8139,39 +8139,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>509996</v>
+        <v>509801</v>
       </c>
       <c r="R70" t="n">
-        <v>7063129</v>
+        <v>7062864</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8214,6 +8209,31 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8230,10 +8250,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121499654</v>
+        <v>121501875</v>
       </c>
       <c r="B71" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8246,34 +8266,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509801</v>
+        <v>510108</v>
       </c>
       <c r="R71" t="n">
-        <v>7062864</v>
+        <v>7063267</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8316,31 +8336,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8357,10 +8352,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121501875</v>
+        <v>121502170</v>
       </c>
       <c r="B72" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8373,34 +8368,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>510108</v>
+        <v>509996</v>
       </c>
       <c r="R72" t="n">
-        <v>7063267</v>
+        <v>7063129</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9909,10 +9909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121513772</v>
+        <v>121511099</v>
       </c>
       <c r="B86" t="n">
-        <v>90716</v>
+        <v>79691</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9925,34 +9925,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>509770</v>
+        <v>509872</v>
       </c>
       <c r="R86" t="n">
-        <v>7063048</v>
+        <v>7063233</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,6 +9987,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9995,6 +10000,31 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10011,10 +10041,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121513387</v>
+        <v>121510322</v>
       </c>
       <c r="B87" t="n">
-        <v>90716</v>
+        <v>57356</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10027,39 +10057,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509837</v>
+        <v>509727</v>
       </c>
       <c r="R87" t="n">
-        <v>7063092</v>
+        <v>7063277</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10102,31 +10132,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10143,10 +10148,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121511099</v>
+        <v>121512362</v>
       </c>
       <c r="B88" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10159,34 +10164,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509872</v>
+        <v>509701</v>
       </c>
       <c r="R88" t="n">
-        <v>7063233</v>
+        <v>7063225</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10221,11 +10231,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10234,31 +10239,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10275,10 +10255,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121512000</v>
+        <v>121513772</v>
       </c>
       <c r="B89" t="n">
-        <v>79690</v>
+        <v>90716</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10291,21 +10271,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10315,10 +10295,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>509850</v>
+        <v>509770</v>
       </c>
       <c r="R89" t="n">
-        <v>7063142</v>
+        <v>7063048</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10377,10 +10357,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121510322</v>
+        <v>121513387</v>
       </c>
       <c r="B90" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10393,39 +10373,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>509727</v>
+        <v>509837</v>
       </c>
       <c r="R90" t="n">
-        <v>7063277</v>
+        <v>7063092</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10468,6 +10448,31 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10484,10 +10489,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121512362</v>
+        <v>121512000</v>
       </c>
       <c r="B91" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10500,39 +10505,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>509701</v>
+        <v>509850</v>
       </c>
       <c r="R91" t="n">
-        <v>7063225</v>
+        <v>7063142</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -13877,10 +13877,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121510935</v>
+        <v>121509893</v>
       </c>
       <c r="B121" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13893,27 +13893,27 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>509840</v>
+        <v>509672</v>
       </c>
       <c r="R121" t="n">
-        <v>7063219</v>
+        <v>7063416</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13968,31 +13968,6 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -14111,10 +14086,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121509893</v>
+        <v>121510935</v>
       </c>
       <c r="B123" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14127,27 +14102,27 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14156,10 +14131,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>509672</v>
+        <v>509840</v>
       </c>
       <c r="R123" t="n">
-        <v>7063416</v>
+        <v>7063219</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14202,6 +14177,31 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
@@ -15497,10 +15497,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121513701</v>
+        <v>121510687</v>
       </c>
       <c r="B136" t="n">
-        <v>74715</v>
+        <v>90716</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15513,34 +15513,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>509762</v>
+        <v>509845</v>
       </c>
       <c r="R136" t="n">
-        <v>7063068</v>
+        <v>7063217</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15599,10 +15599,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121510638</v>
+        <v>121513701</v>
       </c>
       <c r="B137" t="n">
-        <v>79690</v>
+        <v>74715</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15615,34 +15615,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>509833</v>
+        <v>509762</v>
       </c>
       <c r="R137" t="n">
-        <v>7063253</v>
+        <v>7063068</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15685,31 +15685,6 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
@@ -15726,10 +15701,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121510687</v>
+        <v>121510638</v>
       </c>
       <c r="B138" t="n">
-        <v>90716</v>
+        <v>79690</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15742,21 +15717,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15766,10 +15741,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>509845</v>
+        <v>509833</v>
       </c>
       <c r="R138" t="n">
-        <v>7063217</v>
+        <v>7063253</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15812,6 +15787,31 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -15828,10 +15828,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121511059</v>
+        <v>121510819</v>
       </c>
       <c r="B139" t="n">
-        <v>79726</v>
+        <v>90738</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15840,43 +15840,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>509872</v>
+        <v>509857</v>
       </c>
       <c r="R139" t="n">
-        <v>7063233</v>
+        <v>7063220</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15919,31 +15914,6 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -15960,10 +15930,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121514245</v>
+        <v>121513550</v>
       </c>
       <c r="B140" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15976,27 +15946,27 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -16005,10 +15975,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>509882</v>
+        <v>509824</v>
       </c>
       <c r="R140" t="n">
-        <v>7062753</v>
+        <v>7063064</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16051,6 +16021,26 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -16067,7 +16057,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121513830</v>
+        <v>121514245</v>
       </c>
       <c r="B141" t="n">
         <v>57356</v>
@@ -16112,10 +16102,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>509790</v>
+        <v>509882</v>
       </c>
       <c r="R141" t="n">
-        <v>7063000</v>
+        <v>7062753</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16174,7 +16164,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121513205</v>
+        <v>121513830</v>
       </c>
       <c r="B142" t="n">
         <v>57356</v>
@@ -16210,7 +16200,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -16219,10 +16209,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>509802</v>
+        <v>509790</v>
       </c>
       <c r="R142" t="n">
-        <v>7063094</v>
+        <v>7063000</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16281,10 +16271,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121510819</v>
+        <v>121513205</v>
       </c>
       <c r="B143" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16297,34 +16287,39 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>509857</v>
+        <v>509802</v>
       </c>
       <c r="R143" t="n">
-        <v>7063220</v>
+        <v>7063094</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16383,10 +16378,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121513550</v>
+        <v>121511059</v>
       </c>
       <c r="B144" t="n">
-        <v>90716</v>
+        <v>79726</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16395,43 +16390,43 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>509824</v>
+        <v>509872</v>
       </c>
       <c r="R144" t="n">
-        <v>7063064</v>
+        <v>7063233</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16475,24 +16470,29 @@
       <c r="AG144" t="b">
         <v>0</v>
       </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121499605</v>
+        <v>121499839</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,39 +2675,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509785</v>
+        <v>509822</v>
       </c>
       <c r="R20" t="n">
-        <v>7062874</v>
+        <v>7062861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,6 +2745,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2766,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121499839</v>
+        <v>121499605</v>
       </c>
       <c r="B21" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2782,34 +2802,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509822</v>
+        <v>509785</v>
       </c>
       <c r="R21" t="n">
-        <v>7062861</v>
+        <v>7062874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,31 +2877,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2893,10 +2893,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121500282</v>
+        <v>121501985</v>
       </c>
       <c r="B22" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,43 +2909,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509915</v>
+        <v>510064</v>
       </c>
       <c r="R22" t="n">
-        <v>7062758</v>
+        <v>7063220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3004,10 +3000,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121501985</v>
+        <v>121500282</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,39 +3016,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510064</v>
+        <v>509915</v>
       </c>
       <c r="R23" t="n">
-        <v>7063220</v>
+        <v>7062758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121501454</v>
+        <v>121501367</v>
       </c>
       <c r="B29" t="n">
-        <v>56560</v>
+        <v>90738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3681,48 +3681,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509999</v>
+        <v>510023</v>
       </c>
       <c r="R29" t="n">
-        <v>7063087</v>
+        <v>7063038</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3765,11 +3751,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3786,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121501367</v>
+        <v>121501887</v>
       </c>
       <c r="B30" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3802,34 +3783,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510023</v>
+        <v>510108</v>
       </c>
       <c r="R30" t="n">
-        <v>7063038</v>
+        <v>7063267</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3888,10 +3869,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121501887</v>
+        <v>121500715</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>57509</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3904,34 +3885,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510108</v>
+        <v>509995</v>
       </c>
       <c r="R31" t="n">
-        <v>7063267</v>
+        <v>7063003</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3974,6 +3969,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121500715</v>
+        <v>121501454</v>
       </c>
       <c r="B36" t="n">
-        <v>57509</v>
+        <v>56560</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4434,21 +4434,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509995</v>
+        <v>509999</v>
       </c>
       <c r="R36" t="n">
-        <v>7063003</v>
+        <v>7063087</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121499946</v>
+        <v>121501666</v>
       </c>
       <c r="B37" t="n">
-        <v>79691</v>
+        <v>90738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4555,34 +4555,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509886</v>
+        <v>509999</v>
       </c>
       <c r="R37" t="n">
-        <v>7062832</v>
+        <v>7063087</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4625,6 +4630,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4641,10 +4671,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121501666</v>
+        <v>121499946</v>
       </c>
       <c r="B38" t="n">
-        <v>90738</v>
+        <v>79691</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4657,39 +4687,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509999</v>
+        <v>509886</v>
       </c>
       <c r="R38" t="n">
-        <v>7063087</v>
+        <v>7062832</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4732,31 +4757,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121502770</v>
+        <v>121500024</v>
       </c>
       <c r="B39" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4789,27 +4789,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4818,10 +4822,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509730</v>
+        <v>509829</v>
       </c>
       <c r="R39" t="n">
-        <v>7063046</v>
+        <v>7062852</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4864,6 +4868,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4880,10 +4909,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121500024</v>
+        <v>121502770</v>
       </c>
       <c r="B40" t="n">
-        <v>90716</v>
+        <v>57356</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4896,31 +4925,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4929,10 +4954,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509829</v>
+        <v>509730</v>
       </c>
       <c r="R40" t="n">
-        <v>7062852</v>
+        <v>7063046</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4975,31 +5000,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121500126</v>
+        <v>121502766</v>
       </c>
       <c r="B41" t="n">
-        <v>79719</v>
+        <v>57356</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5028,38 +5028,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509872</v>
+        <v>509728</v>
       </c>
       <c r="R41" t="n">
-        <v>7062810</v>
+        <v>7063047</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5118,10 +5123,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121502766</v>
+        <v>121501377</v>
       </c>
       <c r="B42" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5134,39 +5139,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509728</v>
+        <v>510023</v>
       </c>
       <c r="R42" t="n">
-        <v>7063047</v>
+        <v>7063038</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5225,10 +5225,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121502591</v>
+        <v>121500126</v>
       </c>
       <c r="B43" t="n">
-        <v>56560</v>
+        <v>79719</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5237,25 +5237,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509769</v>
+        <v>509872</v>
       </c>
       <c r="R43" t="n">
-        <v>7063041</v>
+        <v>7062810</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5327,10 +5327,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121501377</v>
+        <v>121502591</v>
       </c>
       <c r="B44" t="n">
-        <v>90720</v>
+        <v>56560</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>510023</v>
+        <v>509769</v>
       </c>
       <c r="R44" t="n">
-        <v>7063038</v>
+        <v>7063041</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6294,10 +6294,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121502557</v>
+        <v>121500038</v>
       </c>
       <c r="B53" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6310,39 +6310,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>509798</v>
+        <v>509829</v>
       </c>
       <c r="R53" t="n">
-        <v>7063019</v>
+        <v>7062852</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6385,6 +6380,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6401,10 +6421,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121499875</v>
+        <v>121503055</v>
       </c>
       <c r="B54" t="n">
-        <v>91403</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6413,38 +6433,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Östra Nyland, Östra Nyland, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>509861</v>
+        <v>509562</v>
       </c>
       <c r="R54" t="n">
-        <v>7062861</v>
+        <v>7063187</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6503,7 +6528,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121499799</v>
+        <v>121502557</v>
       </c>
       <c r="B55" t="n">
         <v>57356</v>
@@ -6548,10 +6573,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>509823</v>
+        <v>509798</v>
       </c>
       <c r="R55" t="n">
-        <v>7062878</v>
+        <v>7063019</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6610,10 +6635,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121499492</v>
+        <v>121499875</v>
       </c>
       <c r="B56" t="n">
-        <v>57356</v>
+        <v>91403</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6622,43 +6647,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>509751</v>
+        <v>509861</v>
       </c>
       <c r="R56" t="n">
-        <v>7062898</v>
+        <v>7062861</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6717,10 +6737,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121500038</v>
+        <v>121499799</v>
       </c>
       <c r="B57" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6733,34 +6753,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>509829</v>
+        <v>509823</v>
       </c>
       <c r="R57" t="n">
-        <v>7062852</v>
+        <v>7062878</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6803,31 +6828,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6844,10 +6844,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121503055</v>
+        <v>121499492</v>
       </c>
       <c r="B58" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6860,39 +6860,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Östra Nyland, Östra Nyland, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>509562</v>
+        <v>509751</v>
       </c>
       <c r="R58" t="n">
-        <v>7063187</v>
+        <v>7062898</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7573,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121500154</v>
+        <v>121499616</v>
       </c>
       <c r="B65" t="n">
-        <v>79691</v>
+        <v>57372</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7589,34 +7589,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>509884</v>
+        <v>509751</v>
       </c>
       <c r="R65" t="n">
-        <v>7062810</v>
+        <v>7062897</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7675,10 +7680,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121499616</v>
+        <v>121499686</v>
       </c>
       <c r="B66" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7691,16 +7696,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7714,16 +7719,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509751</v>
+        <v>509801</v>
       </c>
       <c r="R66" t="n">
-        <v>7062897</v>
+        <v>7062864</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7766,6 +7776,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7782,10 +7817,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121499686</v>
+        <v>121502443</v>
       </c>
       <c r="B67" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7798,44 +7833,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509801</v>
+        <v>509834</v>
       </c>
       <c r="R67" t="n">
-        <v>7062864</v>
+        <v>7063042</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7878,31 +7903,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7919,10 +7919,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121502443</v>
+        <v>121500154</v>
       </c>
       <c r="B68" t="n">
-        <v>90716</v>
+        <v>79691</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7935,21 +7935,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509834</v>
+        <v>509884</v>
       </c>
       <c r="R68" t="n">
-        <v>7063042</v>
+        <v>7062810</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8021,10 +8021,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121503173</v>
+        <v>121501875</v>
       </c>
       <c r="B69" t="n">
-        <v>79690</v>
+        <v>90738</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8037,21 +8037,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>509569</v>
+        <v>510108</v>
       </c>
       <c r="R69" t="n">
-        <v>7063250</v>
+        <v>7063267</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8123,10 +8123,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121499654</v>
+        <v>121503173</v>
       </c>
       <c r="B70" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8139,34 +8139,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>509801</v>
+        <v>509569</v>
       </c>
       <c r="R70" t="n">
-        <v>7062864</v>
+        <v>7063250</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8209,31 +8209,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8250,10 +8225,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121501875</v>
+        <v>121502170</v>
       </c>
       <c r="B71" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8266,34 +8241,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>510108</v>
+        <v>509996</v>
       </c>
       <c r="R71" t="n">
-        <v>7063267</v>
+        <v>7063129</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8352,10 +8332,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121502170</v>
+        <v>121499654</v>
       </c>
       <c r="B72" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8368,39 +8348,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509996</v>
+        <v>509801</v>
       </c>
       <c r="R72" t="n">
-        <v>7063129</v>
+        <v>7062864</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8443,6 +8418,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8677,10 +8677,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121513266</v>
+        <v>121510352</v>
       </c>
       <c r="B75" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8693,34 +8693,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509678</v>
+        <v>509738</v>
       </c>
       <c r="R75" t="n">
-        <v>7063166</v>
+        <v>7063269</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8763,31 +8763,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8804,7 +8779,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121509494</v>
+        <v>121513266</v>
       </c>
       <c r="B76" t="n">
         <v>78609</v>
@@ -8840,14 +8815,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>509623</v>
+        <v>509678</v>
       </c>
       <c r="R76" t="n">
-        <v>7063243</v>
+        <v>7063166</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8931,10 +8906,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121510373</v>
+        <v>121509494</v>
       </c>
       <c r="B77" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8947,39 +8922,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>509730</v>
+        <v>509623</v>
       </c>
       <c r="R77" t="n">
-        <v>7063271</v>
+        <v>7063243</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9030,22 +9000,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9063,7 +9033,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121512881</v>
+        <v>121510373</v>
       </c>
       <c r="B78" t="n">
         <v>79690</v>
@@ -9097,16 +9067,21 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>509766</v>
+        <v>509730</v>
       </c>
       <c r="R78" t="n">
-        <v>7063137</v>
+        <v>7063271</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9141,11 +9116,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9154,6 +9124,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Salix caprea</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9170,10 +9165,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121510352</v>
+        <v>121512881</v>
       </c>
       <c r="B79" t="n">
-        <v>90716</v>
+        <v>79690</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9186,34 +9181,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>509738</v>
+        <v>509766</v>
       </c>
       <c r="R79" t="n">
-        <v>7063269</v>
+        <v>7063137</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9246,6 +9241,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9909,10 +9909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121511099</v>
+        <v>121512000</v>
       </c>
       <c r="B86" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9925,34 +9925,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>509872</v>
+        <v>509850</v>
       </c>
       <c r="R86" t="n">
-        <v>7063233</v>
+        <v>7063142</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,11 +9987,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10000,31 +9995,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10041,10 +10011,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121510322</v>
+        <v>121513772</v>
       </c>
       <c r="B87" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10057,39 +10027,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509727</v>
+        <v>509770</v>
       </c>
       <c r="R87" t="n">
-        <v>7063277</v>
+        <v>7063048</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10148,10 +10113,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121512362</v>
+        <v>121513387</v>
       </c>
       <c r="B88" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10164,39 +10129,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509701</v>
+        <v>509837</v>
       </c>
       <c r="R88" t="n">
-        <v>7063225</v>
+        <v>7063092</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10239,6 +10204,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10255,10 +10245,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121513772</v>
+        <v>121511099</v>
       </c>
       <c r="B89" t="n">
-        <v>90716</v>
+        <v>79691</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10271,34 +10261,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>509770</v>
+        <v>509872</v>
       </c>
       <c r="R89" t="n">
-        <v>7063048</v>
+        <v>7063233</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10333,6 +10323,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10341,6 +10336,31 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10357,10 +10377,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121513387</v>
+        <v>121510322</v>
       </c>
       <c r="B90" t="n">
-        <v>90716</v>
+        <v>57356</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10373,39 +10393,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>509837</v>
+        <v>509727</v>
       </c>
       <c r="R90" t="n">
-        <v>7063092</v>
+        <v>7063277</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10448,31 +10468,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10489,10 +10484,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121512000</v>
+        <v>121512362</v>
       </c>
       <c r="B91" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10505,34 +10500,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>509850</v>
+        <v>509701</v>
       </c>
       <c r="R91" t="n">
-        <v>7063142</v>
+        <v>7063225</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11505,10 +11505,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121509895</v>
+        <v>121509421</v>
       </c>
       <c r="B100" t="n">
-        <v>57356</v>
+        <v>74715</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11521,39 +11521,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>509672</v>
+        <v>509608</v>
       </c>
       <c r="R100" t="n">
-        <v>7063419</v>
+        <v>7063256</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11612,10 +11607,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121511816</v>
+        <v>121510607</v>
       </c>
       <c r="B101" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11624,43 +11619,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>509794</v>
+        <v>509826</v>
       </c>
       <c r="R101" t="n">
-        <v>7063242</v>
+        <v>7063254</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11719,10 +11709,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121513947</v>
+        <v>121512085</v>
       </c>
       <c r="B102" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11735,39 +11725,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>509796</v>
+        <v>509811</v>
       </c>
       <c r="R102" t="n">
-        <v>7062825</v>
+        <v>7063166</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11826,10 +11811,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121509950</v>
+        <v>121512479</v>
       </c>
       <c r="B103" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11842,39 +11827,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>509687</v>
+        <v>509676</v>
       </c>
       <c r="R103" t="n">
-        <v>7063429</v>
+        <v>7063208</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11933,10 +11913,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121512085</v>
+        <v>121509895</v>
       </c>
       <c r="B104" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11949,34 +11929,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>509811</v>
+        <v>509672</v>
       </c>
       <c r="R104" t="n">
-        <v>7063166</v>
+        <v>7063419</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12035,10 +12020,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121512479</v>
+        <v>121511816</v>
       </c>
       <c r="B105" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12051,34 +12036,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>509676</v>
+        <v>509794</v>
       </c>
       <c r="R105" t="n">
-        <v>7063208</v>
+        <v>7063242</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12137,10 +12127,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121509421</v>
+        <v>121513947</v>
       </c>
       <c r="B106" t="n">
-        <v>74715</v>
+        <v>57356</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12153,34 +12143,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>509608</v>
+        <v>509796</v>
       </c>
       <c r="R106" t="n">
-        <v>7063256</v>
+        <v>7062825</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12239,10 +12234,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121510607</v>
+        <v>121509950</v>
       </c>
       <c r="B107" t="n">
-        <v>79719</v>
+        <v>57356</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12251,38 +12246,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>509826</v>
+        <v>509687</v>
       </c>
       <c r="R107" t="n">
-        <v>7063254</v>
+        <v>7063429</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13877,10 +13877,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121509893</v>
+        <v>121510935</v>
       </c>
       <c r="B121" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13893,27 +13893,27 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>509672</v>
+        <v>509840</v>
       </c>
       <c r="R121" t="n">
-        <v>7063416</v>
+        <v>7063219</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13968,6 +13968,31 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -14086,10 +14111,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121510935</v>
+        <v>121509893</v>
       </c>
       <c r="B123" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14102,27 +14127,27 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14131,10 +14156,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>509840</v>
+        <v>509672</v>
       </c>
       <c r="R123" t="n">
-        <v>7063219</v>
+        <v>7063416</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14177,31 +14202,6 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
@@ -14218,10 +14218,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121510016</v>
+        <v>121514280</v>
       </c>
       <c r="B124" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14234,34 +14234,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>509723</v>
+        <v>509889</v>
       </c>
       <c r="R124" t="n">
-        <v>7063385</v>
+        <v>7062729</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14320,10 +14325,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121514280</v>
+        <v>121510016</v>
       </c>
       <c r="B125" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14336,39 +14341,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>509889</v>
+        <v>509723</v>
       </c>
       <c r="R125" t="n">
-        <v>7062729</v>
+        <v>7063385</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16612,10 +16612,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121512309</v>
+        <v>121513877</v>
       </c>
       <c r="B146" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16628,27 +16628,27 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16657,10 +16657,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>509781</v>
+        <v>509777</v>
       </c>
       <c r="R146" t="n">
-        <v>7063131</v>
+        <v>7062985</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16721,12 +16721,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -16744,10 +16744,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121509673</v>
+        <v>121512309</v>
       </c>
       <c r="B147" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16760,16 +16760,16 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -16777,36 +16777,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>509703</v>
+        <v>509781</v>
       </c>
       <c r="R147" t="n">
-        <v>7063387</v>
+        <v>7063131</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16849,6 +16835,31 @@
       </c>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -16865,7 +16876,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121510877</v>
+        <v>121509673</v>
       </c>
       <c r="B148" t="n">
         <v>57356</v>
@@ -16898,10 +16909,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16910,10 +16935,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>509859</v>
+        <v>509703</v>
       </c>
       <c r="R148" t="n">
-        <v>7063248</v>
+        <v>7063387</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16972,10 +16997,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121513877</v>
+        <v>121510877</v>
       </c>
       <c r="B149" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16988,39 +17013,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>509777</v>
+        <v>509859</v>
       </c>
       <c r="R149" t="n">
-        <v>7062985</v>
+        <v>7063248</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17063,31 +17088,6 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -17338,10 +17338,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121510833</v>
+        <v>121510620</v>
       </c>
       <c r="B152" t="n">
-        <v>56560</v>
+        <v>79725</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17350,52 +17350,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>509857</v>
+        <v>509826</v>
       </c>
       <c r="R152" t="n">
-        <v>7063220</v>
+        <v>7063254</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17454,10 +17440,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121513546</v>
+        <v>121511810</v>
       </c>
       <c r="B153" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17470,37 +17456,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>509815</v>
+        <v>509809</v>
       </c>
       <c r="R153" t="n">
-        <v>7063064</v>
+        <v>7063240</v>
       </c>
       <c r="S153" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17556,10 +17547,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121510620</v>
+        <v>121510833</v>
       </c>
       <c r="B154" t="n">
-        <v>79725</v>
+        <v>56560</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17568,38 +17559,52 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>509826</v>
+        <v>509857</v>
       </c>
       <c r="R154" t="n">
-        <v>7063254</v>
+        <v>7063220</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17658,10 +17663,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121512290</v>
+        <v>121513546</v>
       </c>
       <c r="B155" t="n">
-        <v>91403</v>
+        <v>82393</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17670,46 +17675,41 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>509781</v>
+        <v>509815</v>
       </c>
       <c r="R155" t="n">
-        <v>7063131</v>
+        <v>7063064</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17749,31 +17749,6 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -17790,10 +17765,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121511810</v>
+        <v>121512290</v>
       </c>
       <c r="B156" t="n">
-        <v>57356</v>
+        <v>91403</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17802,43 +17777,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>509809</v>
+        <v>509781</v>
       </c>
       <c r="R156" t="n">
-        <v>7063240</v>
+        <v>7063131</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17881,6 +17856,31 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -3096,10 +3096,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121501890</v>
+        <v>121502443</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>90724</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3112,39 +3112,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510108</v>
+        <v>509834</v>
       </c>
       <c r="R24" t="n">
-        <v>7063268</v>
+        <v>7063042</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,10 +3198,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121502443</v>
+        <v>121501890</v>
       </c>
       <c r="B25" t="n">
-        <v>90724</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,34 +3214,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509834</v>
+        <v>510108</v>
       </c>
       <c r="R25" t="n">
-        <v>7063042</v>
+        <v>7063268</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3549,10 +3549,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121502031</v>
+        <v>121500139</v>
       </c>
       <c r="B28" t="n">
-        <v>74722</v>
+        <v>79733</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3561,38 +3561,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510054</v>
+        <v>509883</v>
       </c>
       <c r="R28" t="n">
-        <v>7063204</v>
+        <v>7062810</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121502928</v>
+        <v>121499843</v>
       </c>
       <c r="B29" t="n">
-        <v>90739</v>
+        <v>90728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3663,25 +3663,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509666</v>
+        <v>509857</v>
       </c>
       <c r="R29" t="n">
-        <v>7063113</v>
+        <v>7062855</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121500139</v>
+        <v>121499605</v>
       </c>
       <c r="B30" t="n">
-        <v>79733</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3765,38 +3765,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509883</v>
+        <v>509785</v>
       </c>
       <c r="R30" t="n">
-        <v>7062810</v>
+        <v>7062874</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3855,10 +3860,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121499843</v>
+        <v>121499942</v>
       </c>
       <c r="B31" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3871,21 +3876,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3895,10 +3900,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509857</v>
+        <v>509886</v>
       </c>
       <c r="R31" t="n">
-        <v>7062855</v>
+        <v>7062840</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3957,10 +3962,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121499942</v>
+        <v>121502031</v>
       </c>
       <c r="B32" t="n">
-        <v>79697</v>
+        <v>74722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3973,34 +3978,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509886</v>
+        <v>510054</v>
       </c>
       <c r="R32" t="n">
-        <v>7062840</v>
+        <v>7063204</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4059,10 +4064,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121499605</v>
+        <v>121502928</v>
       </c>
       <c r="B33" t="n">
-        <v>57357</v>
+        <v>90739</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4071,43 +4076,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509785</v>
+        <v>509666</v>
       </c>
       <c r="R33" t="n">
-        <v>7062874</v>
+        <v>7063113</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121499884</v>
+        <v>121500282</v>
       </c>
       <c r="B36" t="n">
-        <v>79697</v>
+        <v>57510</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4396,34 +4396,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509829</v>
+        <v>509915</v>
       </c>
       <c r="R36" t="n">
-        <v>7062852</v>
+        <v>7062758</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4458,11 +4467,6 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4471,31 +4475,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Populus tremula</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4512,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121499799</v>
+        <v>121499884</v>
       </c>
       <c r="B37" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4528,39 +4507,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509823</v>
+        <v>509829</v>
       </c>
       <c r="R37" t="n">
-        <v>7062878</v>
+        <v>7062852</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4595,6 +4569,11 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4603,6 +4582,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Populus tremula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4619,10 +4623,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121500282</v>
+        <v>121499799</v>
       </c>
       <c r="B38" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4635,31 +4639,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509915</v>
+        <v>509823</v>
       </c>
       <c r="R38" t="n">
-        <v>7062758</v>
+        <v>7062878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4730,10 +4730,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121502697</v>
+        <v>121503055</v>
       </c>
       <c r="B39" t="n">
-        <v>74714</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4746,34 +4746,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Östra Nyland, Östra Nyland, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509752</v>
+        <v>509562</v>
       </c>
       <c r="R39" t="n">
-        <v>7063041</v>
+        <v>7063187</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4832,10 +4837,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121501875</v>
+        <v>121503173</v>
       </c>
       <c r="B40" t="n">
-        <v>90746</v>
+        <v>79697</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4848,21 +4853,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4872,10 +4877,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>510108</v>
+        <v>509569</v>
       </c>
       <c r="R40" t="n">
-        <v>7063267</v>
+        <v>7063250</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4934,10 +4939,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121499738</v>
+        <v>121501875</v>
       </c>
       <c r="B41" t="n">
-        <v>74722</v>
+        <v>90746</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4950,34 +4955,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509823</v>
+        <v>510108</v>
       </c>
       <c r="R41" t="n">
-        <v>7062862</v>
+        <v>7063267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5036,10 +5041,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121501187</v>
+        <v>121502697</v>
       </c>
       <c r="B42" t="n">
-        <v>98113</v>
+        <v>74714</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5048,42 +5053,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509999</v>
+        <v>509752</v>
       </c>
       <c r="R42" t="n">
-        <v>7062970</v>
+        <v>7063041</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5142,10 +5143,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121503055</v>
+        <v>121499738</v>
       </c>
       <c r="B43" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5158,39 +5159,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Östra Nyland, Östra Nyland, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509562</v>
+        <v>509823</v>
       </c>
       <c r="R43" t="n">
-        <v>7063187</v>
+        <v>7062862</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5249,10 +5245,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121503173</v>
+        <v>121501187</v>
       </c>
       <c r="B44" t="n">
-        <v>79697</v>
+        <v>98113</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5261,38 +5257,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509569</v>
+        <v>509999</v>
       </c>
       <c r="R44" t="n">
-        <v>7063250</v>
+        <v>7062970</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121500197</v>
+        <v>121499643</v>
       </c>
       <c r="B53" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6252,39 +6252,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>509923</v>
+        <v>509815</v>
       </c>
       <c r="R53" t="n">
-        <v>7062805</v>
+        <v>7062883</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6343,7 +6338,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121501376</v>
+        <v>121499578</v>
       </c>
       <c r="B54" t="n">
         <v>57357</v>
@@ -6388,10 +6383,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>510023</v>
+        <v>509760</v>
       </c>
       <c r="R54" t="n">
-        <v>7063038</v>
+        <v>7062882</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6450,7 +6445,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121501256</v>
+        <v>121500197</v>
       </c>
       <c r="B55" t="n">
         <v>57357</v>
@@ -6495,10 +6490,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>509991</v>
+        <v>509923</v>
       </c>
       <c r="R55" t="n">
-        <v>7062974</v>
+        <v>7062805</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6557,7 +6552,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121502766</v>
+        <v>121501376</v>
       </c>
       <c r="B56" t="n">
         <v>57357</v>
@@ -6602,10 +6597,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>509728</v>
+        <v>510023</v>
       </c>
       <c r="R56" t="n">
-        <v>7063047</v>
+        <v>7063038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6664,7 +6659,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121499578</v>
+        <v>121501256</v>
       </c>
       <c r="B57" t="n">
         <v>57357</v>
@@ -6709,10 +6704,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>509760</v>
+        <v>509991</v>
       </c>
       <c r="R57" t="n">
-        <v>7062882</v>
+        <v>7062974</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6771,10 +6766,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121499643</v>
+        <v>121502766</v>
       </c>
       <c r="B58" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6787,34 +6782,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>509815</v>
+        <v>509728</v>
       </c>
       <c r="R58" t="n">
-        <v>7062883</v>
+        <v>7063047</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6873,10 +6873,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121499875</v>
+        <v>121502801</v>
       </c>
       <c r="B59" t="n">
-        <v>91411</v>
+        <v>57357</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6885,38 +6885,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>509861</v>
+        <v>509714</v>
       </c>
       <c r="R59" t="n">
-        <v>7062861</v>
+        <v>7063026</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6975,10 +6980,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121499616</v>
+        <v>121500431</v>
       </c>
       <c r="B60" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6991,16 +6996,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7008,10 +7013,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7020,10 +7034,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>509751</v>
+        <v>509890</v>
       </c>
       <c r="R60" t="n">
-        <v>7062897</v>
+        <v>7062735</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7066,6 +7080,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7082,10 +7121,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121499654</v>
+        <v>121499875</v>
       </c>
       <c r="B61" t="n">
-        <v>78616</v>
+        <v>91411</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7094,25 +7133,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7122,10 +7161,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>509801</v>
+        <v>509861</v>
       </c>
       <c r="R61" t="n">
-        <v>7062864</v>
+        <v>7062861</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7168,31 +7207,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7209,10 +7223,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121499492</v>
+        <v>121499654</v>
       </c>
       <c r="B62" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7225,39 +7239,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>509751</v>
+        <v>509801</v>
       </c>
       <c r="R62" t="n">
-        <v>7062898</v>
+        <v>7062864</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7300,6 +7309,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7316,10 +7350,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121502801</v>
+        <v>121499616</v>
       </c>
       <c r="B63" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7332,16 +7366,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7361,10 +7395,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>509714</v>
+        <v>509751</v>
       </c>
       <c r="R63" t="n">
-        <v>7063026</v>
+        <v>7062897</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7423,7 +7457,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121500431</v>
+        <v>121499492</v>
       </c>
       <c r="B64" t="n">
         <v>57357</v>
@@ -7456,19 +7490,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7477,10 +7502,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>509890</v>
+        <v>509751</v>
       </c>
       <c r="R64" t="n">
-        <v>7062735</v>
+        <v>7062898</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7523,31 +7548,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8006,10 +8006,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121502932</v>
+        <v>121499686</v>
       </c>
       <c r="B69" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8022,16 +8022,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8042,7 +8042,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>509772</v>
+        <v>509801</v>
       </c>
       <c r="R69" t="n">
-        <v>7063098</v>
+        <v>7062864</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8106,6 +8106,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8123,10 +8143,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121499686</v>
+        <v>121502932</v>
       </c>
       <c r="B70" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8139,16 +8159,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8159,7 +8179,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8173,10 +8193,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>509801</v>
+        <v>509772</v>
       </c>
       <c r="R70" t="n">
-        <v>7062864</v>
+        <v>7063098</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8223,26 +8243,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -10848,10 +10848,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121510352</v>
+        <v>121511816</v>
       </c>
       <c r="B95" t="n">
-        <v>90724</v>
+        <v>57357</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10864,34 +10864,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>509738</v>
+        <v>509794</v>
       </c>
       <c r="R95" t="n">
-        <v>7063269</v>
+        <v>7063242</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11164,10 +11169,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121511816</v>
+        <v>121510352</v>
       </c>
       <c r="B98" t="n">
-        <v>57357</v>
+        <v>90724</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11180,39 +11185,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>509794</v>
+        <v>509738</v>
       </c>
       <c r="R98" t="n">
-        <v>7063242</v>
+        <v>7063269</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12105,10 +12105,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121512665</v>
+        <v>121512881</v>
       </c>
       <c r="B106" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12121,21 +12121,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12145,10 +12145,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>509678</v>
+        <v>509766</v>
       </c>
       <c r="R106" t="n">
-        <v>7063166</v>
+        <v>7063137</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12183,6 +12183,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12191,31 +12196,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12232,10 +12212,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121512994</v>
+        <v>121510935</v>
       </c>
       <c r="B107" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12248,39 +12228,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>509678</v>
+        <v>509840</v>
       </c>
       <c r="R107" t="n">
-        <v>7063166</v>
+        <v>7063219</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12331,22 +12311,22 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12364,10 +12344,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121512881</v>
+        <v>121512994</v>
       </c>
       <c r="B108" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12380,34 +12360,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>509766</v>
+        <v>509678</v>
       </c>
       <c r="R108" t="n">
-        <v>7063137</v>
+        <v>7063166</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12442,11 +12427,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12455,6 +12435,31 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12471,10 +12476,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121510935</v>
+        <v>121512665</v>
       </c>
       <c r="B109" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12487,39 +12492,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>509840</v>
+        <v>509678</v>
       </c>
       <c r="R109" t="n">
-        <v>7063219</v>
+        <v>7063166</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12570,22 +12570,22 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12603,10 +12603,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121512309</v>
+        <v>121510373</v>
       </c>
       <c r="B110" t="n">
-        <v>57373</v>
+        <v>79697</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12619,39 +12619,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>509781</v>
+        <v>509730</v>
       </c>
       <c r="R110" t="n">
-        <v>7063131</v>
+        <v>7063271</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12702,22 +12702,22 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Salix caprea</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12735,10 +12735,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121510373</v>
+        <v>121512202</v>
       </c>
       <c r="B111" t="n">
-        <v>79697</v>
+        <v>74722</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12751,39 +12751,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>509730</v>
+        <v>509783</v>
       </c>
       <c r="R111" t="n">
-        <v>7063271</v>
+        <v>7063144</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12826,31 +12821,6 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Salix caprea</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13198,10 +13168,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121512202</v>
+        <v>121513119</v>
       </c>
       <c r="B115" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13214,34 +13184,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>509783</v>
+        <v>509745</v>
       </c>
       <c r="R115" t="n">
-        <v>7063144</v>
+        <v>7063108</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13300,10 +13275,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121513119</v>
+        <v>121512309</v>
       </c>
       <c r="B116" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13316,16 +13291,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -13336,7 +13311,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13345,10 +13320,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>509745</v>
+        <v>509781</v>
       </c>
       <c r="R116" t="n">
-        <v>7063108</v>
+        <v>7063131</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13391,6 +13366,31 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -13870,10 +13870,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121512000</v>
+        <v>121513387</v>
       </c>
       <c r="B121" t="n">
-        <v>79697</v>
+        <v>90724</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13886,34 +13886,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>509850</v>
+        <v>509837</v>
       </c>
       <c r="R121" t="n">
-        <v>7063142</v>
+        <v>7063092</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13956,6 +13961,31 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -13972,10 +14002,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121513387</v>
+        <v>121513877</v>
       </c>
       <c r="B122" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13988,27 +14018,27 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14017,10 +14047,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>509837</v>
+        <v>509777</v>
       </c>
       <c r="R122" t="n">
-        <v>7063092</v>
+        <v>7062985</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14081,12 +14111,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14104,10 +14134,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121513877</v>
+        <v>121510877</v>
       </c>
       <c r="B123" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14120,39 +14150,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>509777</v>
+        <v>509859</v>
       </c>
       <c r="R123" t="n">
-        <v>7062985</v>
+        <v>7063248</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14195,31 +14225,6 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
@@ -14236,7 +14241,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121510877</v>
+        <v>121512903</v>
       </c>
       <c r="B124" t="n">
         <v>57357</v>
@@ -14272,19 +14277,19 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>509859</v>
+        <v>509758</v>
       </c>
       <c r="R124" t="n">
-        <v>7063248</v>
+        <v>7063118</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14343,10 +14348,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121512903</v>
+        <v>121512000</v>
       </c>
       <c r="B125" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14359,39 +14364,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>509758</v>
+        <v>509850</v>
       </c>
       <c r="R125" t="n">
-        <v>7063118</v>
+        <v>7063142</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14450,10 +14450,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121512363</v>
+        <v>121512479</v>
       </c>
       <c r="B126" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14466,39 +14466,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>509704</v>
+        <v>509676</v>
       </c>
       <c r="R126" t="n">
-        <v>7063224</v>
+        <v>7063208</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14557,10 +14552,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121512479</v>
+        <v>121512363</v>
       </c>
       <c r="B127" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14573,34 +14568,39 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>509676</v>
+        <v>509704</v>
       </c>
       <c r="R127" t="n">
-        <v>7063208</v>
+        <v>7063224</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14659,7 +14659,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121514712</v>
+        <v>121513175</v>
       </c>
       <c r="B128" t="n">
         <v>57357</v>
@@ -14695,7 +14695,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>509680</v>
+        <v>509794</v>
       </c>
       <c r="R128" t="n">
-        <v>7063096</v>
+        <v>7063114</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121513175</v>
+        <v>121514712</v>
       </c>
       <c r="B129" t="n">
         <v>57357</v>
@@ -14802,7 +14802,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>509794</v>
+        <v>509680</v>
       </c>
       <c r="R129" t="n">
-        <v>7063114</v>
+        <v>7063096</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15773,10 +15773,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121511099</v>
+        <v>121509587</v>
       </c>
       <c r="B138" t="n">
-        <v>79698</v>
+        <v>57373</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15789,34 +15789,43 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>509872</v>
+        <v>509623</v>
       </c>
       <c r="R138" t="n">
-        <v>7063233</v>
+        <v>7063364</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15851,11 +15860,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -15864,31 +15868,6 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -15905,10 +15884,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121510253</v>
+        <v>121512467</v>
       </c>
       <c r="B139" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15921,21 +15900,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15945,10 +15924,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>509663</v>
+        <v>509687</v>
       </c>
       <c r="R139" t="n">
-        <v>7063347</v>
+        <v>7063193</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15983,6 +15962,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15991,31 +15975,6 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -16032,10 +15991,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121509417</v>
+        <v>121511099</v>
       </c>
       <c r="B140" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16048,39 +16007,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>509606</v>
+        <v>509872</v>
       </c>
       <c r="R140" t="n">
-        <v>7063266</v>
+        <v>7063233</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16115,6 +16069,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -16123,6 +16082,31 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -16139,10 +16123,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121509587</v>
+        <v>121510253</v>
       </c>
       <c r="B141" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16155,43 +16139,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>509623</v>
+        <v>509663</v>
       </c>
       <c r="R141" t="n">
-        <v>7063364</v>
+        <v>7063347</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16234,6 +16209,31 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -16250,10 +16250,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121512467</v>
+        <v>121509417</v>
       </c>
       <c r="B142" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16266,34 +16266,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>509687</v>
+        <v>509606</v>
       </c>
       <c r="R142" t="n">
-        <v>7063193</v>
+        <v>7063266</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16326,11 +16331,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16357,10 +16357,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121510016</v>
+        <v>121514280</v>
       </c>
       <c r="B143" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16373,34 +16373,39 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>509723</v>
+        <v>509889</v>
       </c>
       <c r="R143" t="n">
-        <v>7063385</v>
+        <v>7062729</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16459,10 +16464,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121509451</v>
+        <v>121510016</v>
       </c>
       <c r="B144" t="n">
-        <v>79697</v>
+        <v>82400</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16475,21 +16480,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16499,10 +16504,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>509661</v>
+        <v>509723</v>
       </c>
       <c r="R144" t="n">
-        <v>7063260</v>
+        <v>7063385</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16561,10 +16566,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121514280</v>
+        <v>121509451</v>
       </c>
       <c r="B145" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16577,39 +16582,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>509889</v>
+        <v>509661</v>
       </c>
       <c r="R145" t="n">
-        <v>7062729</v>
+        <v>7063260</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17304,10 +17304,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121513947</v>
+        <v>121510201</v>
       </c>
       <c r="B152" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17320,39 +17320,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>509796</v>
+        <v>509782</v>
       </c>
       <c r="R152" t="n">
-        <v>7062825</v>
+        <v>7063393</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17411,10 +17406,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121511034</v>
+        <v>121513947</v>
       </c>
       <c r="B153" t="n">
-        <v>79732</v>
+        <v>57357</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17423,43 +17418,43 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>509872</v>
+        <v>509796</v>
       </c>
       <c r="R153" t="n">
-        <v>7063233</v>
+        <v>7062825</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17502,31 +17497,6 @@
       </c>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -17543,10 +17513,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121510799</v>
+        <v>121511034</v>
       </c>
       <c r="B154" t="n">
-        <v>79697</v>
+        <v>79732</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17555,31 +17525,31 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -17588,10 +17558,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>509846</v>
+        <v>509872</v>
       </c>
       <c r="R154" t="n">
-        <v>7063221</v>
+        <v>7063233</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17634,6 +17604,31 @@
       </c>
       <c r="AG154" t="b">
         <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
@@ -17650,10 +17645,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121509655</v>
+        <v>121510799</v>
       </c>
       <c r="B155" t="n">
-        <v>57510</v>
+        <v>79697</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17666,36 +17661,27 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17704,10 +17690,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>509663</v>
+        <v>509846</v>
       </c>
       <c r="R155" t="n">
-        <v>7063347</v>
+        <v>7063221</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17750,11 +17736,6 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -17771,10 +17752,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121510201</v>
+        <v>121509655</v>
       </c>
       <c r="B156" t="n">
-        <v>90728</v>
+        <v>57510</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17787,34 +17768,48 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>509782</v>
+        <v>509663</v>
       </c>
       <c r="R156" t="n">
-        <v>7063393</v>
+        <v>7063347</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17857,6 +17852,11 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
@@ -18077,10 +18077,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121513350</v>
+        <v>121512362</v>
       </c>
       <c r="B159" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18093,39 +18093,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>509837</v>
+        <v>509701</v>
       </c>
       <c r="R159" t="n">
-        <v>7063092</v>
+        <v>7063225</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18168,31 +18168,6 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
@@ -18209,10 +18184,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121512362</v>
+        <v>121510661</v>
       </c>
       <c r="B160" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18225,39 +18200,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>509701</v>
+        <v>509840</v>
       </c>
       <c r="R160" t="n">
-        <v>7063225</v>
+        <v>7063229</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18316,10 +18286,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121510661</v>
+        <v>121514198</v>
       </c>
       <c r="B161" t="n">
-        <v>90746</v>
+        <v>56561</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18332,34 +18302,48 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>509840</v>
+        <v>509877</v>
       </c>
       <c r="R161" t="n">
-        <v>7063229</v>
+        <v>7062713</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18418,10 +18402,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121514198</v>
+        <v>121513350</v>
       </c>
       <c r="B162" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18434,36 +18418,27 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18472,10 +18447,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>509877</v>
+        <v>509837</v>
       </c>
       <c r="R162" t="n">
-        <v>7062713</v>
+        <v>7063092</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18518,6 +18493,31 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -3651,10 +3651,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121499843</v>
+        <v>121502031</v>
       </c>
       <c r="B29" t="n">
-        <v>90728</v>
+        <v>74722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3667,34 +3667,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509857</v>
+        <v>510054</v>
       </c>
       <c r="R29" t="n">
-        <v>7062855</v>
+        <v>7063204</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121499605</v>
+        <v>121502928</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>90739</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3765,43 +3765,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509785</v>
+        <v>509666</v>
       </c>
       <c r="R30" t="n">
-        <v>7062874</v>
+        <v>7063113</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3860,10 +3855,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121499942</v>
+        <v>121499843</v>
       </c>
       <c r="B31" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3876,21 +3871,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3900,10 +3895,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509886</v>
+        <v>509857</v>
       </c>
       <c r="R31" t="n">
-        <v>7062840</v>
+        <v>7062855</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,10 +3957,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121502031</v>
+        <v>121499605</v>
       </c>
       <c r="B32" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3978,34 +3973,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510054</v>
+        <v>509785</v>
       </c>
       <c r="R32" t="n">
-        <v>7063204</v>
+        <v>7062874</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121502928</v>
+        <v>121499942</v>
       </c>
       <c r="B33" t="n">
-        <v>90739</v>
+        <v>79697</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4076,25 +4076,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509666</v>
+        <v>509886</v>
       </c>
       <c r="R33" t="n">
-        <v>7063113</v>
+        <v>7062840</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121500282</v>
+        <v>121499884</v>
       </c>
       <c r="B36" t="n">
-        <v>57510</v>
+        <v>79697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4396,43 +4396,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509915</v>
+        <v>509829</v>
       </c>
       <c r="R36" t="n">
-        <v>7062758</v>
+        <v>7062852</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,6 +4458,11 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4475,6 +4471,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Populus tremula</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4491,10 +4512,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121499884</v>
+        <v>121499799</v>
       </c>
       <c r="B37" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4507,34 +4528,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509829</v>
+        <v>509823</v>
       </c>
       <c r="R37" t="n">
-        <v>7062852</v>
+        <v>7062878</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4569,11 +4595,6 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4582,31 +4603,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Populus tremula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4623,10 +4619,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121499799</v>
+        <v>121500282</v>
       </c>
       <c r="B38" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4639,27 +4635,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509823</v>
+        <v>509915</v>
       </c>
       <c r="R38" t="n">
-        <v>7062878</v>
+        <v>7062758</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -12105,10 +12105,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121512881</v>
+        <v>121512665</v>
       </c>
       <c r="B106" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12121,21 +12121,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12145,10 +12145,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>509766</v>
+        <v>509678</v>
       </c>
       <c r="R106" t="n">
-        <v>7063137</v>
+        <v>7063166</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12183,11 +12183,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12196,6 +12191,31 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12212,10 +12232,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121510935</v>
+        <v>121512994</v>
       </c>
       <c r="B107" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12228,39 +12248,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>509840</v>
+        <v>509678</v>
       </c>
       <c r="R107" t="n">
-        <v>7063219</v>
+        <v>7063166</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12311,22 +12331,22 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12344,10 +12364,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121512994</v>
+        <v>121512881</v>
       </c>
       <c r="B108" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12360,39 +12380,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>509678</v>
+        <v>509766</v>
       </c>
       <c r="R108" t="n">
-        <v>7063166</v>
+        <v>7063137</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12427,6 +12442,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12435,31 +12455,6 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12476,10 +12471,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121512665</v>
+        <v>121510935</v>
       </c>
       <c r="B109" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12492,34 +12487,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>509678</v>
+        <v>509840</v>
       </c>
       <c r="R109" t="n">
-        <v>7063166</v>
+        <v>7063219</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12570,22 +12570,22 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12603,10 +12603,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121510373</v>
+        <v>121512309</v>
       </c>
       <c r="B110" t="n">
-        <v>79697</v>
+        <v>57373</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12619,39 +12619,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>509730</v>
+        <v>509781</v>
       </c>
       <c r="R110" t="n">
-        <v>7063271</v>
+        <v>7063131</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12702,22 +12702,22 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12735,10 +12735,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121512202</v>
+        <v>121510373</v>
       </c>
       <c r="B111" t="n">
-        <v>74722</v>
+        <v>79697</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12751,34 +12751,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>509783</v>
+        <v>509730</v>
       </c>
       <c r="R111" t="n">
-        <v>7063144</v>
+        <v>7063271</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12821,6 +12826,31 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Salix caprea</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13168,10 +13198,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121513119</v>
+        <v>121512202</v>
       </c>
       <c r="B115" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13184,39 +13214,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>509745</v>
+        <v>509783</v>
       </c>
       <c r="R115" t="n">
-        <v>7063108</v>
+        <v>7063144</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13275,10 +13300,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121512309</v>
+        <v>121513119</v>
       </c>
       <c r="B116" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13291,16 +13316,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -13311,7 +13336,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13320,10 +13345,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>509781</v>
+        <v>509745</v>
       </c>
       <c r="R116" t="n">
-        <v>7063131</v>
+        <v>7063108</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13366,31 +13391,6 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -13407,10 +13407,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121510881</v>
+        <v>121512169</v>
       </c>
       <c r="B117" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13423,39 +13423,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>509857</v>
+        <v>509872</v>
       </c>
       <c r="R117" t="n">
-        <v>7063220</v>
+        <v>7063233</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13498,6 +13493,31 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -13514,10 +13534,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121513772</v>
+        <v>121510638</v>
       </c>
       <c r="B118" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13530,34 +13550,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>509770</v>
+        <v>509833</v>
       </c>
       <c r="R118" t="n">
-        <v>7063048</v>
+        <v>7063253</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13600,6 +13620,31 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13616,10 +13661,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121512169</v>
+        <v>121513772</v>
       </c>
       <c r="B119" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13632,34 +13677,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>509872</v>
+        <v>509770</v>
       </c>
       <c r="R119" t="n">
-        <v>7063233</v>
+        <v>7063048</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13702,31 +13747,6 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -13743,10 +13763,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121510638</v>
+        <v>121510881</v>
       </c>
       <c r="B120" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13759,34 +13779,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>509833</v>
+        <v>509857</v>
       </c>
       <c r="R120" t="n">
-        <v>7063253</v>
+        <v>7063220</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13829,31 +13854,6 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -13870,10 +13870,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121513387</v>
+        <v>121512000</v>
       </c>
       <c r="B121" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13886,39 +13886,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>509837</v>
+        <v>509850</v>
       </c>
       <c r="R121" t="n">
-        <v>7063092</v>
+        <v>7063142</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13961,31 +13956,6 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -14002,10 +13972,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121513877</v>
+        <v>121513387</v>
       </c>
       <c r="B122" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14018,27 +13988,27 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14047,10 +14017,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>509777</v>
+        <v>509837</v>
       </c>
       <c r="R122" t="n">
-        <v>7062985</v>
+        <v>7063092</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14111,12 +14081,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14134,10 +14104,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121510877</v>
+        <v>121513877</v>
       </c>
       <c r="B123" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14150,39 +14120,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>509859</v>
+        <v>509777</v>
       </c>
       <c r="R123" t="n">
-        <v>7063248</v>
+        <v>7062985</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14225,6 +14195,31 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
@@ -14241,7 +14236,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121512903</v>
+        <v>121510877</v>
       </c>
       <c r="B124" t="n">
         <v>57357</v>
@@ -14277,19 +14272,19 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>509758</v>
+        <v>509859</v>
       </c>
       <c r="R124" t="n">
-        <v>7063118</v>
+        <v>7063248</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14348,10 +14343,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121512000</v>
+        <v>121512903</v>
       </c>
       <c r="B125" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14364,34 +14359,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>509850</v>
+        <v>509758</v>
       </c>
       <c r="R125" t="n">
-        <v>7063142</v>
+        <v>7063118</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16357,10 +16357,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121514280</v>
+        <v>121510016</v>
       </c>
       <c r="B143" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16373,39 +16373,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>509889</v>
+        <v>509723</v>
       </c>
       <c r="R143" t="n">
-        <v>7062729</v>
+        <v>7063385</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16464,10 +16459,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121510016</v>
+        <v>121509451</v>
       </c>
       <c r="B144" t="n">
-        <v>82400</v>
+        <v>79697</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16480,21 +16475,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16504,10 +16499,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>509723</v>
+        <v>509661</v>
       </c>
       <c r="R144" t="n">
-        <v>7063385</v>
+        <v>7063260</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16566,10 +16561,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121509451</v>
+        <v>121514280</v>
       </c>
       <c r="B145" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16582,34 +16577,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>509661</v>
+        <v>509889</v>
       </c>
       <c r="R145" t="n">
-        <v>7063260</v>
+        <v>7062729</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -2871,10 +2871,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121501367</v>
+        <v>121500038</v>
       </c>
       <c r="B22" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2887,21 +2887,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510023</v>
+        <v>509829</v>
       </c>
       <c r="R22" t="n">
-        <v>7063038</v>
+        <v>7062852</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,6 +2957,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2973,7 +2998,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121501666</v>
+        <v>121501367</v>
       </c>
       <c r="B23" t="n">
         <v>90746</v>
@@ -3007,21 +3032,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509999</v>
+        <v>510023</v>
       </c>
       <c r="R23" t="n">
-        <v>7063087</v>
+        <v>7063038</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,31 +3084,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3105,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121500392</v>
+        <v>121501666</v>
       </c>
       <c r="B24" t="n">
-        <v>74713</v>
+        <v>90746</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3117,38 +3112,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509922</v>
+        <v>509999</v>
       </c>
       <c r="R24" t="n">
-        <v>7062815</v>
+        <v>7063087</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3191,6 +3191,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3207,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121500038</v>
+        <v>121499735</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3223,21 +3248,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3247,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509829</v>
+        <v>509823</v>
       </c>
       <c r="R25" t="n">
-        <v>7062852</v>
+        <v>7062863</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,31 +3318,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3334,10 +3334,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121499735</v>
+        <v>121500392</v>
       </c>
       <c r="B26" t="n">
-        <v>82400</v>
+        <v>74713</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3346,25 +3346,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509823</v>
+        <v>509922</v>
       </c>
       <c r="R26" t="n">
-        <v>7062863</v>
+        <v>7062815</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121502697</v>
+        <v>121501887</v>
       </c>
       <c r="B27" t="n">
-        <v>74714</v>
+        <v>90728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3452,34 +3452,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509752</v>
+        <v>510108</v>
       </c>
       <c r="R27" t="n">
-        <v>7063041</v>
+        <v>7063267</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121501887</v>
+        <v>121502697</v>
       </c>
       <c r="B28" t="n">
-        <v>90728</v>
+        <v>74714</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3554,34 +3554,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510108</v>
+        <v>509752</v>
       </c>
       <c r="R28" t="n">
-        <v>7063267</v>
+        <v>7063041</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -5079,10 +5079,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121502031</v>
+        <v>121499578</v>
       </c>
       <c r="B42" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5095,34 +5095,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510054</v>
+        <v>509760</v>
       </c>
       <c r="R42" t="n">
-        <v>7063204</v>
+        <v>7062882</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5181,10 +5186,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121499578</v>
+        <v>121502031</v>
       </c>
       <c r="B43" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5197,39 +5202,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509760</v>
+        <v>510054</v>
       </c>
       <c r="R43" t="n">
-        <v>7062882</v>
+        <v>7063204</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6042,10 +6042,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121502443</v>
+        <v>121501985</v>
       </c>
       <c r="B51" t="n">
-        <v>90724</v>
+        <v>57357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6058,34 +6058,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509834</v>
+        <v>510064</v>
       </c>
       <c r="R51" t="n">
-        <v>7063042</v>
+        <v>7063220</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6144,7 +6149,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121501985</v>
+        <v>121500134</v>
       </c>
       <c r="B52" t="n">
         <v>57357</v>
@@ -6183,16 +6188,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>510064</v>
+        <v>509829</v>
       </c>
       <c r="R52" t="n">
-        <v>7063220</v>
+        <v>7062852</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6235,6 +6245,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6251,10 +6286,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121500134</v>
+        <v>121502443</v>
       </c>
       <c r="B53" t="n">
-        <v>57357</v>
+        <v>90724</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6267,44 +6302,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>509829</v>
+        <v>509834</v>
       </c>
       <c r="R53" t="n">
-        <v>7062852</v>
+        <v>7063042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6347,31 +6372,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7558,10 +7558,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121499738</v>
+        <v>121500197</v>
       </c>
       <c r="B65" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7574,34 +7574,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>509823</v>
+        <v>509923</v>
       </c>
       <c r="R65" t="n">
-        <v>7062862</v>
+        <v>7062805</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7660,7 +7665,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121500197</v>
+        <v>121501586</v>
       </c>
       <c r="B66" t="n">
         <v>57357</v>
@@ -7696,7 +7701,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7705,10 +7710,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509923</v>
+        <v>510062</v>
       </c>
       <c r="R66" t="n">
-        <v>7062805</v>
+        <v>7063168</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7767,10 +7772,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121501586</v>
+        <v>121499738</v>
       </c>
       <c r="B67" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7783,39 +7788,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>510062</v>
+        <v>509823</v>
       </c>
       <c r="R67" t="n">
-        <v>7063168</v>
+        <v>7062862</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8224,10 +8224,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121500119</v>
+        <v>121501553</v>
       </c>
       <c r="B71" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8240,34 +8240,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509883</v>
+        <v>510053</v>
       </c>
       <c r="R71" t="n">
-        <v>7062821</v>
+        <v>7063157</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8326,7 +8331,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121501553</v>
+        <v>121502766</v>
       </c>
       <c r="B72" t="n">
         <v>57357</v>
@@ -8362,7 +8367,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8371,10 +8376,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>510053</v>
+        <v>509728</v>
       </c>
       <c r="R72" t="n">
-        <v>7063157</v>
+        <v>7063047</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8433,10 +8438,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121502766</v>
+        <v>121500119</v>
       </c>
       <c r="B73" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8449,39 +8454,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509728</v>
+        <v>509883</v>
       </c>
       <c r="R73" t="n">
-        <v>7063047</v>
+        <v>7062821</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8677,10 +8677,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121512479</v>
+        <v>121509587</v>
       </c>
       <c r="B75" t="n">
-        <v>82400</v>
+        <v>57373</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8693,34 +8693,43 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509676</v>
+        <v>509623</v>
       </c>
       <c r="R75" t="n">
-        <v>7063208</v>
+        <v>7063364</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8886,10 +8895,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121510607</v>
+        <v>121512479</v>
       </c>
       <c r="B77" t="n">
-        <v>79726</v>
+        <v>82400</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8898,25 +8907,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8926,10 +8935,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>509826</v>
+        <v>509676</v>
       </c>
       <c r="R77" t="n">
-        <v>7063254</v>
+        <v>7063208</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8988,10 +8997,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121509587</v>
+        <v>121510607</v>
       </c>
       <c r="B78" t="n">
-        <v>57373</v>
+        <v>79726</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9000,47 +9009,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>509623</v>
+        <v>509826</v>
       </c>
       <c r="R78" t="n">
-        <v>7063364</v>
+        <v>7063254</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121513546</v>
+        <v>121513795</v>
       </c>
       <c r="B79" t="n">
-        <v>82400</v>
+        <v>90693</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9111,41 +9111,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>509815</v>
+        <v>509761</v>
       </c>
       <c r="R79" t="n">
-        <v>7063064</v>
+        <v>7063058</v>
       </c>
       <c r="S79" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9185,6 +9190,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9201,10 +9231,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121513795</v>
+        <v>121509421</v>
       </c>
       <c r="B80" t="n">
-        <v>90693</v>
+        <v>74722</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9213,43 +9243,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509761</v>
+        <v>509608</v>
       </c>
       <c r="R80" t="n">
-        <v>7063058</v>
+        <v>7063256</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9292,31 +9317,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9333,10 +9333,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121509421</v>
+        <v>121510799</v>
       </c>
       <c r="B81" t="n">
-        <v>74722</v>
+        <v>79697</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9349,34 +9349,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509608</v>
+        <v>509846</v>
       </c>
       <c r="R81" t="n">
-        <v>7063256</v>
+        <v>7063221</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9435,10 +9440,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121510799</v>
+        <v>121513546</v>
       </c>
       <c r="B82" t="n">
-        <v>79697</v>
+        <v>82400</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9451,42 +9456,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509846</v>
+        <v>509815</v>
       </c>
       <c r="R82" t="n">
-        <v>7063221</v>
+        <v>7063064</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121511803</v>
+        <v>121512881</v>
       </c>
       <c r="B88" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10083,34 +10083,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509872</v>
+        <v>509766</v>
       </c>
       <c r="R88" t="n">
-        <v>7063233</v>
+        <v>7063137</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10145,6 +10145,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10153,31 +10158,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10194,10 +10174,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121512881</v>
+        <v>121511803</v>
       </c>
       <c r="B89" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10210,34 +10190,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>509766</v>
+        <v>509872</v>
       </c>
       <c r="R89" t="n">
-        <v>7063137</v>
+        <v>7063233</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10272,11 +10252,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10285,6 +10260,31 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10301,10 +10301,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121510881</v>
+        <v>121513266</v>
       </c>
       <c r="B90" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10317,39 +10317,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>509857</v>
+        <v>509678</v>
       </c>
       <c r="R90" t="n">
-        <v>7063220</v>
+        <v>7063166</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10392,6 +10387,31 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10408,10 +10428,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121513830</v>
+        <v>121511869</v>
       </c>
       <c r="B91" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10424,39 +10444,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>509790</v>
+        <v>509783</v>
       </c>
       <c r="R91" t="n">
-        <v>7063000</v>
+        <v>7063234</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10515,10 +10530,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121509893</v>
+        <v>121512202</v>
       </c>
       <c r="B92" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10531,39 +10546,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>509672</v>
+        <v>509783</v>
       </c>
       <c r="R92" t="n">
-        <v>7063416</v>
+        <v>7063144</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10622,10 +10632,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121511869</v>
+        <v>121510881</v>
       </c>
       <c r="B93" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10638,34 +10648,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>509783</v>
+        <v>509857</v>
       </c>
       <c r="R93" t="n">
-        <v>7063234</v>
+        <v>7063220</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10724,10 +10739,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121513266</v>
+        <v>121513830</v>
       </c>
       <c r="B94" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10740,34 +10755,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>509678</v>
+        <v>509790</v>
       </c>
       <c r="R94" t="n">
-        <v>7063166</v>
+        <v>7063000</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10810,31 +10830,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -10851,10 +10846,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121512202</v>
+        <v>121509893</v>
       </c>
       <c r="B95" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10867,34 +10862,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>509783</v>
+        <v>509672</v>
       </c>
       <c r="R95" t="n">
-        <v>7063144</v>
+        <v>7063416</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11498,10 +11498,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121509895</v>
+        <v>121510819</v>
       </c>
       <c r="B101" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11514,39 +11514,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>509672</v>
+        <v>509857</v>
       </c>
       <c r="R101" t="n">
-        <v>7063419</v>
+        <v>7063220</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11605,10 +11600,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121513947</v>
+        <v>121509655</v>
       </c>
       <c r="B102" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11621,39 +11616,48 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>509796</v>
+        <v>509663</v>
       </c>
       <c r="R102" t="n">
-        <v>7062825</v>
+        <v>7063347</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11696,6 +11700,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11712,7 +11721,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121510877</v>
+        <v>121509895</v>
       </c>
       <c r="B103" t="n">
         <v>57357</v>
@@ -11748,7 +11757,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11757,10 +11766,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>509859</v>
+        <v>509672</v>
       </c>
       <c r="R103" t="n">
-        <v>7063248</v>
+        <v>7063419</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11819,10 +11828,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121510819</v>
+        <v>121513947</v>
       </c>
       <c r="B104" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11835,34 +11844,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>509857</v>
+        <v>509796</v>
       </c>
       <c r="R104" t="n">
-        <v>7063220</v>
+        <v>7062825</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11921,10 +11935,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121510620</v>
+        <v>121510877</v>
       </c>
       <c r="B105" t="n">
-        <v>79732</v>
+        <v>57357</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11933,38 +11947,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>509826</v>
+        <v>509859</v>
       </c>
       <c r="R105" t="n">
-        <v>7063254</v>
+        <v>7063248</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12023,10 +12042,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121509655</v>
+        <v>121510620</v>
       </c>
       <c r="B106" t="n">
-        <v>57510</v>
+        <v>79732</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12035,52 +12054,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>509663</v>
+        <v>509826</v>
       </c>
       <c r="R106" t="n">
-        <v>7063347</v>
+        <v>7063254</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12123,11 +12128,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -14824,10 +14824,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121513350</v>
+        <v>121513701</v>
       </c>
       <c r="B130" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14840,39 +14840,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>509837</v>
+        <v>509762</v>
       </c>
       <c r="R130" t="n">
-        <v>7063092</v>
+        <v>7063068</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14915,31 +14910,6 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -14956,10 +14926,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121513701</v>
+        <v>121513350</v>
       </c>
       <c r="B131" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14972,34 +14942,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>509762</v>
+        <v>509837</v>
       </c>
       <c r="R131" t="n">
-        <v>7063068</v>
+        <v>7063092</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15042,6 +15017,31 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
@@ -15058,10 +15058,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121512782</v>
+        <v>121513387</v>
       </c>
       <c r="B132" t="n">
-        <v>74714</v>
+        <v>90724</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15074,34 +15074,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>509731</v>
+        <v>509837</v>
       </c>
       <c r="R132" t="n">
-        <v>7063132</v>
+        <v>7063092</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15144,6 +15149,31 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
@@ -15160,10 +15190,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121513387</v>
+        <v>121512309</v>
       </c>
       <c r="B133" t="n">
-        <v>90724</v>
+        <v>57373</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15176,27 +15206,27 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15205,10 +15235,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>509837</v>
+        <v>509781</v>
       </c>
       <c r="R133" t="n">
-        <v>7063092</v>
+        <v>7063131</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15269,12 +15299,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15292,10 +15322,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121514198</v>
+        <v>121509673</v>
       </c>
       <c r="B134" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15308,16 +15338,16 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -15327,7 +15357,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -15335,6 +15365,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -15342,14 +15377,14 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>509877</v>
+        <v>509703</v>
       </c>
       <c r="R134" t="n">
-        <v>7062713</v>
+        <v>7063387</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15408,10 +15443,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121512309</v>
+        <v>121512782</v>
       </c>
       <c r="B135" t="n">
-        <v>57373</v>
+        <v>74714</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15424,39 +15459,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>509781</v>
+        <v>509731</v>
       </c>
       <c r="R135" t="n">
-        <v>7063131</v>
+        <v>7063132</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15499,31 +15529,6 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -15540,10 +15545,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121509673</v>
+        <v>121514198</v>
       </c>
       <c r="B136" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15556,16 +15561,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -15575,7 +15580,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -15583,11 +15588,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -15595,14 +15595,14 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>509703</v>
+        <v>509877</v>
       </c>
       <c r="R136" t="n">
-        <v>7063387</v>
+        <v>7062713</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15661,10 +15661,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121512199</v>
+        <v>121514712</v>
       </c>
       <c r="B137" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15677,34 +15677,39 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>509781</v>
+        <v>509680</v>
       </c>
       <c r="R137" t="n">
-        <v>7063145</v>
+        <v>7063096</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15763,7 +15768,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121514712</v>
+        <v>121511810</v>
       </c>
       <c r="B138" t="n">
         <v>57357</v>
@@ -15799,19 +15804,19 @@
       <c r="I138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>509680</v>
+        <v>509809</v>
       </c>
       <c r="R138" t="n">
-        <v>7063096</v>
+        <v>7063240</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15870,7 +15875,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121511810</v>
+        <v>121513119</v>
       </c>
       <c r="B139" t="n">
         <v>57357</v>
@@ -15911,14 +15916,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>509809</v>
+        <v>509745</v>
       </c>
       <c r="R139" t="n">
-        <v>7063240</v>
+        <v>7063108</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15977,10 +15982,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121513119</v>
+        <v>121512199</v>
       </c>
       <c r="B140" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15993,39 +15998,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>509745</v>
+        <v>509781</v>
       </c>
       <c r="R140" t="n">
-        <v>7063108</v>
+        <v>7063145</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16343,10 +16343,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121512968</v>
+        <v>121513870</v>
       </c>
       <c r="B143" t="n">
-        <v>90746</v>
+        <v>56561</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16359,34 +16359,48 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>509750</v>
+        <v>509786</v>
       </c>
       <c r="R143" t="n">
-        <v>7063102</v>
+        <v>7062954</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16445,7 +16459,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121513870</v>
+        <v>121510833</v>
       </c>
       <c r="B144" t="n">
         <v>56561</v>
@@ -16495,14 +16509,14 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>509786</v>
+        <v>509857</v>
       </c>
       <c r="R144" t="n">
-        <v>7062954</v>
+        <v>7063220</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16561,10 +16575,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121510833</v>
+        <v>121512620</v>
       </c>
       <c r="B145" t="n">
-        <v>56561</v>
+        <v>57510</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16577,21 +16591,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -16599,26 +16613,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>509857</v>
+        <v>509672</v>
       </c>
       <c r="R145" t="n">
-        <v>7063220</v>
+        <v>7063185</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16661,6 +16675,11 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -16677,7 +16696,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121512620</v>
+        <v>121509418</v>
       </c>
       <c r="B146" t="n">
         <v>57510</v>
@@ -16720,21 +16739,16 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>509672</v>
+        <v>509603</v>
       </c>
       <c r="R146" t="n">
-        <v>7063185</v>
+        <v>7063266</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16777,11 +16791,6 @@
       </c>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -16798,10 +16807,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121509418</v>
+        <v>121512968</v>
       </c>
       <c r="B147" t="n">
-        <v>57510</v>
+        <v>90746</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16814,43 +16823,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>509603</v>
+        <v>509750</v>
       </c>
       <c r="R147" t="n">
-        <v>7063266</v>
+        <v>7063102</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17016,10 +17016,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121511816</v>
+        <v>121510687</v>
       </c>
       <c r="B149" t="n">
-        <v>57357</v>
+        <v>90724</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17032,39 +17032,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>509794</v>
+        <v>509845</v>
       </c>
       <c r="R149" t="n">
-        <v>7063242</v>
+        <v>7063217</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17123,10 +17118,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121510687</v>
+        <v>121511034</v>
       </c>
       <c r="B150" t="n">
-        <v>90724</v>
+        <v>79732</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17135,38 +17130,43 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>509845</v>
+        <v>509872</v>
       </c>
       <c r="R150" t="n">
-        <v>7063217</v>
+        <v>7063233</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17209,6 +17209,31 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -17225,10 +17250,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121511034</v>
+        <v>121510638</v>
       </c>
       <c r="B151" t="n">
-        <v>79732</v>
+        <v>79697</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17237,43 +17262,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>509872</v>
+        <v>509833</v>
       </c>
       <c r="R151" t="n">
-        <v>7063233</v>
+        <v>7063253</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17324,22 +17344,22 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -17357,10 +17377,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121510638</v>
+        <v>121511816</v>
       </c>
       <c r="B152" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17373,34 +17393,39 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>509833</v>
+        <v>509794</v>
       </c>
       <c r="R152" t="n">
-        <v>7063253</v>
+        <v>7063242</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17443,31 +17468,6 @@
       </c>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -938,7 +938,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121501376</v>
+        <v>121503091</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -974,19 +974,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Östra Nyland, Östra Nyland, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510023</v>
+        <v>509565</v>
       </c>
       <c r="R4" t="n">
-        <v>7063038</v>
+        <v>7063172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121503091</v>
+        <v>121501376</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1081,19 +1081,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Nyland, Östra Nyland, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509565</v>
+        <v>510023</v>
       </c>
       <c r="R5" t="n">
-        <v>7063172</v>
+        <v>7063038</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121502932</v>
+        <v>121501377</v>
       </c>
       <c r="B8" t="n">
-        <v>56561</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,44 +1402,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509772</v>
+        <v>510023</v>
       </c>
       <c r="R8" t="n">
-        <v>7063098</v>
+        <v>7063038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,11 +1472,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1503,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121501454</v>
+        <v>121500119</v>
       </c>
       <c r="B9" t="n">
-        <v>56561</v>
+        <v>79697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,48 +1504,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509999</v>
+        <v>509883</v>
       </c>
       <c r="R9" t="n">
-        <v>7063087</v>
+        <v>7062821</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,11 +1574,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1624,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121501377</v>
+        <v>121502684</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1664,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510023</v>
+        <v>509752</v>
       </c>
       <c r="R10" t="n">
-        <v>7063038</v>
+        <v>7063039</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1940,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121500119</v>
+        <v>121502932</v>
       </c>
       <c r="B13" t="n">
-        <v>79697</v>
+        <v>56561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,34 +1922,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509883</v>
+        <v>509772</v>
       </c>
       <c r="R13" t="n">
-        <v>7062821</v>
+        <v>7063098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,6 +2002,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2042,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121502684</v>
+        <v>121501454</v>
       </c>
       <c r="B14" t="n">
-        <v>90746</v>
+        <v>56561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,34 +2039,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509752</v>
+        <v>509999</v>
       </c>
       <c r="R14" t="n">
-        <v>7063039</v>
+        <v>7063087</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,6 +2123,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121500126</v>
+        <v>121501985</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2924,38 +2924,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509872</v>
+        <v>510064</v>
       </c>
       <c r="R22" t="n">
-        <v>7062810</v>
+        <v>7063220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3014,10 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121500139</v>
+        <v>121501394</v>
       </c>
       <c r="B23" t="n">
-        <v>79733</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3026,38 +3031,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509883</v>
+        <v>510035</v>
       </c>
       <c r="R23" t="n">
-        <v>7062810</v>
+        <v>7063074</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3359,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121501985</v>
+        <v>121500126</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3371,43 +3381,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510064</v>
+        <v>509872</v>
       </c>
       <c r="R26" t="n">
-        <v>7063220</v>
+        <v>7062810</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3466,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121501394</v>
+        <v>121500139</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
+        <v>79733</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3478,43 +3483,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510035</v>
+        <v>509883</v>
       </c>
       <c r="R27" t="n">
-        <v>7063074</v>
+        <v>7062810</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121503055</v>
+        <v>121502766</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4241,39 +4241,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Östra Nyland, Östra Nyland, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509562</v>
+        <v>509728</v>
       </c>
       <c r="R34" t="n">
-        <v>7063187</v>
+        <v>7063047</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4332,10 +4332,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121500282</v>
+        <v>121503055</v>
       </c>
       <c r="B35" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4348,43 +4348,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Östra Nyland, Östra Nyland, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509915</v>
+        <v>509562</v>
       </c>
       <c r="R35" t="n">
-        <v>7062758</v>
+        <v>7063187</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4443,10 +4439,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121502766</v>
+        <v>121500555</v>
       </c>
       <c r="B36" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4459,27 +4455,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4488,10 +4484,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509728</v>
+        <v>509882</v>
       </c>
       <c r="R36" t="n">
-        <v>7063047</v>
+        <v>7062734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4534,6 +4530,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4550,10 +4571,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121500555</v>
+        <v>121500282</v>
       </c>
       <c r="B37" t="n">
-        <v>90746</v>
+        <v>57510</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4566,27 +4587,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4595,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509882</v>
+        <v>509915</v>
       </c>
       <c r="R37" t="n">
-        <v>7062734</v>
+        <v>7062758</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4641,31 +4666,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4682,10 +4682,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121499643</v>
+        <v>121501586</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4698,34 +4698,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509815</v>
+        <v>510062</v>
       </c>
       <c r="R38" t="n">
-        <v>7062883</v>
+        <v>7063168</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4784,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121501586</v>
+        <v>121499643</v>
       </c>
       <c r="B39" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4800,39 +4805,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>510062</v>
+        <v>509815</v>
       </c>
       <c r="R39" t="n">
-        <v>7063168</v>
+        <v>7062883</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121501187</v>
+        <v>121501553</v>
       </c>
       <c r="B45" t="n">
-        <v>98113</v>
+        <v>57357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5427,30 +5427,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5459,10 +5460,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>509999</v>
+        <v>510053</v>
       </c>
       <c r="R45" t="n">
-        <v>7062970</v>
+        <v>7063157</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5521,10 +5522,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121499654</v>
+        <v>121502789</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5537,34 +5538,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509801</v>
+        <v>509714</v>
       </c>
       <c r="R46" t="n">
-        <v>7062864</v>
+        <v>7063027</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5607,31 +5613,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5648,10 +5629,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121501553</v>
+        <v>121501187</v>
       </c>
       <c r="B47" t="n">
-        <v>57357</v>
+        <v>98113</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5660,31 +5641,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5693,10 +5673,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>510053</v>
+        <v>509999</v>
       </c>
       <c r="R47" t="n">
-        <v>7063157</v>
+        <v>7062970</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5755,10 +5735,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121502789</v>
+        <v>121499654</v>
       </c>
       <c r="B48" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5771,39 +5751,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>509714</v>
+        <v>509801</v>
       </c>
       <c r="R48" t="n">
-        <v>7063027</v>
+        <v>7062864</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5846,6 +5821,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5964,10 +5964,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121501529</v>
+        <v>121503226</v>
       </c>
       <c r="B50" t="n">
-        <v>90728</v>
+        <v>90724</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5980,34 +5980,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>510058</v>
+        <v>509545</v>
       </c>
       <c r="R50" t="n">
-        <v>7063153</v>
+        <v>7063237</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6066,10 +6066,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121500134</v>
+        <v>121501529</v>
       </c>
       <c r="B51" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6082,44 +6082,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509829</v>
+        <v>510058</v>
       </c>
       <c r="R51" t="n">
-        <v>7062852</v>
+        <v>7063153</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6162,31 +6152,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6203,10 +6168,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121503226</v>
+        <v>121500134</v>
       </c>
       <c r="B52" t="n">
-        <v>90724</v>
+        <v>57357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6219,34 +6184,44 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>509545</v>
+        <v>509829</v>
       </c>
       <c r="R52" t="n">
-        <v>7063237</v>
+        <v>7062852</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6289,6 +6264,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -10356,10 +10356,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121513429</v>
+        <v>121513550</v>
       </c>
       <c r="B90" t="n">
-        <v>57373</v>
+        <v>90724</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10372,27 +10372,27 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10401,13 +10401,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>509803</v>
+        <v>509824</v>
       </c>
       <c r="R90" t="n">
-        <v>7063032</v>
+        <v>7063064</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10447,6 +10447,26 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10463,10 +10483,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121513550</v>
+        <v>121510016</v>
       </c>
       <c r="B91" t="n">
-        <v>90724</v>
+        <v>82400</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10479,39 +10499,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>509824</v>
+        <v>509723</v>
       </c>
       <c r="R91" t="n">
-        <v>7063064</v>
+        <v>7063385</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10554,26 +10569,6 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10590,10 +10585,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121510016</v>
+        <v>121513429</v>
       </c>
       <c r="B92" t="n">
-        <v>82400</v>
+        <v>57373</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10606,37 +10601,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>509723</v>
+        <v>509803</v>
       </c>
       <c r="R92" t="n">
-        <v>7063385</v>
+        <v>7063032</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11465,10 +11465,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121510603</v>
+        <v>121510607</v>
       </c>
       <c r="B100" t="n">
-        <v>79698</v>
+        <v>79726</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11477,25 +11477,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11567,10 +11567,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121510607</v>
+        <v>121510603</v>
       </c>
       <c r="B101" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11579,25 +11579,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11669,10 +11669,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121513877</v>
+        <v>121510935</v>
       </c>
       <c r="B102" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11685,39 +11685,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>509777</v>
+        <v>509840</v>
       </c>
       <c r="R102" t="n">
-        <v>7062985</v>
+        <v>7063219</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11768,22 +11768,22 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11801,10 +11801,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121510935</v>
+        <v>121512670</v>
       </c>
       <c r="B103" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11817,39 +11817,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>509840</v>
+        <v>509744</v>
       </c>
       <c r="R103" t="n">
-        <v>7063219</v>
+        <v>7063125</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11892,31 +11887,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11933,10 +11903,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121512670</v>
+        <v>121513877</v>
       </c>
       <c r="B104" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11949,34 +11919,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>509744</v>
+        <v>509777</v>
       </c>
       <c r="R104" t="n">
-        <v>7063125</v>
+        <v>7062985</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12019,6 +11994,31 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -15647,10 +15647,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121509417</v>
+        <v>121511099</v>
       </c>
       <c r="B137" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15663,39 +15663,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>509606</v>
+        <v>509872</v>
       </c>
       <c r="R137" t="n">
-        <v>7063266</v>
+        <v>7063233</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15730,6 +15725,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -15738,6 +15738,31 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
@@ -15754,10 +15779,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121512881</v>
+        <v>121509418</v>
       </c>
       <c r="B138" t="n">
-        <v>79697</v>
+        <v>57510</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15770,34 +15795,43 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>509766</v>
+        <v>509603</v>
       </c>
       <c r="R138" t="n">
-        <v>7063137</v>
+        <v>7063266</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15830,11 +15864,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15861,10 +15890,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121509418</v>
+        <v>121509417</v>
       </c>
       <c r="B139" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15877,31 +15906,27 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -15910,7 +15935,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>509603</v>
+        <v>509606</v>
       </c>
       <c r="R139" t="n">
         <v>7063266</v>
@@ -15972,10 +15997,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121511099</v>
+        <v>121512881</v>
       </c>
       <c r="B140" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15988,34 +16013,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>509872</v>
+        <v>509766</v>
       </c>
       <c r="R140" t="n">
-        <v>7063233</v>
+        <v>7063137</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16052,7 +16077,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>På en grovbarkad sälglåga.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16063,31 +16088,6 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -17188,10 +17188,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121513870</v>
+        <v>121512577</v>
       </c>
       <c r="B151" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17204,48 +17204,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>509786</v>
+        <v>509672</v>
       </c>
       <c r="R151" t="n">
-        <v>7062954</v>
+        <v>7063185</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17288,6 +17274,31 @@
       </c>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -17304,10 +17315,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121509655</v>
+        <v>121513546</v>
       </c>
       <c r="B152" t="n">
-        <v>57510</v>
+        <v>82400</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17320,51 +17331,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>509663</v>
+        <v>509815</v>
       </c>
       <c r="R152" t="n">
-        <v>7063347</v>
+        <v>7063064</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17404,11 +17401,6 @@
       </c>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -17425,10 +17417,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121512577</v>
+        <v>121514712</v>
       </c>
       <c r="B153" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17441,34 +17433,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>509672</v>
+        <v>509680</v>
       </c>
       <c r="R153" t="n">
-        <v>7063185</v>
+        <v>7063096</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17511,31 +17508,6 @@
       </c>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -17552,10 +17524,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121513546</v>
+        <v>121509673</v>
       </c>
       <c r="B154" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17568,37 +17540,56 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>509815</v>
+        <v>509703</v>
       </c>
       <c r="R154" t="n">
-        <v>7063064</v>
+        <v>7063387</v>
       </c>
       <c r="S154" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17654,10 +17645,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121514712</v>
+        <v>121510615</v>
       </c>
       <c r="B155" t="n">
-        <v>57357</v>
+        <v>79733</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17666,43 +17657,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>509680</v>
+        <v>509826</v>
       </c>
       <c r="R155" t="n">
-        <v>7063096</v>
+        <v>7063254</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17761,10 +17747,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121509673</v>
+        <v>121513795</v>
       </c>
       <c r="B156" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17773,57 +17759,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>509703</v>
+        <v>509761</v>
       </c>
       <c r="R156" t="n">
-        <v>7063387</v>
+        <v>7063058</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17866,6 +17838,31 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
@@ -17882,10 +17879,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121510615</v>
+        <v>121513870</v>
       </c>
       <c r="B157" t="n">
-        <v>79733</v>
+        <v>56561</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17894,38 +17891,52 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>509826</v>
+        <v>509786</v>
       </c>
       <c r="R157" t="n">
-        <v>7063254</v>
+        <v>7062954</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17984,10 +17995,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121513795</v>
+        <v>121509655</v>
       </c>
       <c r="B158" t="n">
-        <v>90693</v>
+        <v>57510</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17996,43 +18007,52 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>509761</v>
+        <v>509663</v>
       </c>
       <c r="R158" t="n">
-        <v>7063058</v>
+        <v>7063347</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18079,26 +18099,6 @@
       <c r="AH158" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -8677,10 +8677,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121511099</v>
+        <v>121512663</v>
       </c>
       <c r="B75" t="n">
-        <v>79698</v>
+        <v>91014</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8693,34 +8693,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509872</v>
+        <v>509744</v>
       </c>
       <c r="R75" t="n">
-        <v>7063233</v>
+        <v>7063125</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8755,11 +8755,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8768,31 +8763,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8809,7 +8779,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121513668</v>
+        <v>121511803</v>
       </c>
       <c r="B76" t="n">
         <v>78616</v>
@@ -8843,21 +8813,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>509824</v>
+        <v>509872</v>
       </c>
       <c r="R76" t="n">
-        <v>7063064</v>
+        <v>7063233</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8941,7 +8906,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121514940</v>
+        <v>121509895</v>
       </c>
       <c r="B77" t="n">
         <v>57357</v>
@@ -8986,10 +8951,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>509622</v>
+        <v>509672</v>
       </c>
       <c r="R77" t="n">
-        <v>7063172</v>
+        <v>7063419</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9048,10 +9013,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121510687</v>
+        <v>121512968</v>
       </c>
       <c r="B78" t="n">
-        <v>90724</v>
+        <v>90746</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9064,34 +9029,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>509845</v>
+        <v>509750</v>
       </c>
       <c r="R78" t="n">
-        <v>7063217</v>
+        <v>7063102</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9150,10 +9115,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121513387</v>
+        <v>121512362</v>
       </c>
       <c r="B79" t="n">
-        <v>90724</v>
+        <v>57357</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9166,39 +9131,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>509837</v>
+        <v>509701</v>
       </c>
       <c r="R79" t="n">
-        <v>7063092</v>
+        <v>7063225</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9241,31 +9206,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9282,10 +9222,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121512665</v>
+        <v>121509673</v>
       </c>
       <c r="B80" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9298,34 +9238,53 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509678</v>
+        <v>509703</v>
       </c>
       <c r="R80" t="n">
-        <v>7063166</v>
+        <v>7063387</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9368,31 +9327,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9409,10 +9343,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121512479</v>
+        <v>121509417</v>
       </c>
       <c r="B81" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9425,34 +9359,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509676</v>
+        <v>509606</v>
       </c>
       <c r="R81" t="n">
-        <v>7063208</v>
+        <v>7063266</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9511,10 +9450,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121509418</v>
+        <v>121513266</v>
       </c>
       <c r="B82" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9527,43 +9466,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509603</v>
+        <v>509678</v>
       </c>
       <c r="R82" t="n">
-        <v>7063266</v>
+        <v>7063166</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9606,6 +9536,31 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9622,10 +9577,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121512782</v>
+        <v>121510429</v>
       </c>
       <c r="B83" t="n">
-        <v>74714</v>
+        <v>78616</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9638,34 +9593,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>509731</v>
+        <v>509795</v>
       </c>
       <c r="R83" t="n">
-        <v>7063132</v>
+        <v>7063275</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9708,6 +9663,31 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9724,10 +9704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121512663</v>
+        <v>121513668</v>
       </c>
       <c r="B84" t="n">
-        <v>91014</v>
+        <v>78616</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9740,34 +9720,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509744</v>
+        <v>509824</v>
       </c>
       <c r="R84" t="n">
-        <v>7063125</v>
+        <v>7063064</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9810,6 +9795,31 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9826,10 +9836,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121510352</v>
+        <v>121510935</v>
       </c>
       <c r="B85" t="n">
-        <v>90724</v>
+        <v>79697</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9842,34 +9852,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509738</v>
+        <v>509840</v>
       </c>
       <c r="R85" t="n">
-        <v>7063269</v>
+        <v>7063219</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9912,6 +9927,31 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9928,7 +9968,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121513947</v>
+        <v>121514240</v>
       </c>
       <c r="B86" t="n">
         <v>57357</v>
@@ -9964,7 +10004,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9973,10 +10013,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>509796</v>
+        <v>509888</v>
       </c>
       <c r="R86" t="n">
-        <v>7062825</v>
+        <v>7062731</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10035,10 +10075,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121512968</v>
+        <v>121513870</v>
       </c>
       <c r="B87" t="n">
-        <v>90746</v>
+        <v>56561</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10051,34 +10091,48 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509750</v>
+        <v>509786</v>
       </c>
       <c r="R87" t="n">
-        <v>7063102</v>
+        <v>7062954</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10137,10 +10191,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121509494</v>
+        <v>121512639</v>
       </c>
       <c r="B88" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10153,34 +10207,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509623</v>
+        <v>509713</v>
       </c>
       <c r="R88" t="n">
-        <v>7063243</v>
+        <v>7063158</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10223,31 +10277,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10264,10 +10293,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121513772</v>
+        <v>121512670</v>
       </c>
       <c r="B89" t="n">
-        <v>90724</v>
+        <v>90728</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10280,21 +10309,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10304,10 +10333,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>509770</v>
+        <v>509744</v>
       </c>
       <c r="R89" t="n">
-        <v>7063048</v>
+        <v>7063125</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10366,10 +10395,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121512639</v>
+        <v>121511059</v>
       </c>
       <c r="B90" t="n">
-        <v>82400</v>
+        <v>79733</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10378,38 +10407,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>509713</v>
+        <v>509872</v>
       </c>
       <c r="R90" t="n">
-        <v>7063158</v>
+        <v>7063233</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10452,6 +10486,31 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10468,10 +10527,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121510016</v>
+        <v>121509587</v>
       </c>
       <c r="B91" t="n">
-        <v>82400</v>
+        <v>57373</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10484,34 +10543,43 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>509723</v>
+        <v>509623</v>
       </c>
       <c r="R91" t="n">
-        <v>7063385</v>
+        <v>7063364</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10570,7 +10638,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121513119</v>
+        <v>121513205</v>
       </c>
       <c r="B92" t="n">
         <v>57357</v>
@@ -10606,7 +10674,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10615,10 +10683,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>509745</v>
+        <v>509802</v>
       </c>
       <c r="R92" t="n">
-        <v>7063108</v>
+        <v>7063094</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10677,10 +10745,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121510373</v>
+        <v>121510201</v>
       </c>
       <c r="B93" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10693,39 +10761,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>509730</v>
+        <v>509782</v>
       </c>
       <c r="R93" t="n">
-        <v>7063271</v>
+        <v>7063393</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10768,31 +10831,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Salix caprea</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -10809,10 +10847,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121514240</v>
+        <v>121510638</v>
       </c>
       <c r="B94" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10825,39 +10863,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>509888</v>
+        <v>509833</v>
       </c>
       <c r="R94" t="n">
-        <v>7062731</v>
+        <v>7063253</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10900,6 +10933,31 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -10916,7 +10974,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121512362</v>
+        <v>121511810</v>
       </c>
       <c r="B95" t="n">
         <v>57357</v>
@@ -10952,7 +11010,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10961,10 +11019,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>509701</v>
+        <v>509809</v>
       </c>
       <c r="R95" t="n">
-        <v>7063225</v>
+        <v>7063240</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11023,10 +11081,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121509421</v>
+        <v>121510661</v>
       </c>
       <c r="B96" t="n">
-        <v>74722</v>
+        <v>90746</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11039,21 +11097,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11063,10 +11121,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>509608</v>
+        <v>509840</v>
       </c>
       <c r="R96" t="n">
-        <v>7063256</v>
+        <v>7063229</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11125,10 +11183,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121512342</v>
+        <v>121512903</v>
       </c>
       <c r="B97" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11141,27 +11199,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11170,10 +11228,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>509781</v>
+        <v>509758</v>
       </c>
       <c r="R97" t="n">
-        <v>7063131</v>
+        <v>7063118</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11216,31 +11274,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11257,10 +11290,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121509673</v>
+        <v>121512085</v>
       </c>
       <c r="B98" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11273,53 +11306,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>509703</v>
+        <v>509811</v>
       </c>
       <c r="R98" t="n">
-        <v>7063387</v>
+        <v>7063166</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11480,10 +11494,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121513009</v>
+        <v>121512202</v>
       </c>
       <c r="B100" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11496,39 +11510,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>509757</v>
+        <v>509783</v>
       </c>
       <c r="R100" t="n">
-        <v>7063103</v>
+        <v>7063144</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11587,10 +11596,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121512363</v>
+        <v>121510253</v>
       </c>
       <c r="B101" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11603,39 +11612,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>509704</v>
+        <v>509663</v>
       </c>
       <c r="R101" t="n">
-        <v>7063224</v>
+        <v>7063347</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11678,6 +11682,31 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11796,10 +11825,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121513877</v>
+        <v>121514280</v>
       </c>
       <c r="B103" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11812,27 +11841,27 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11841,10 +11870,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>509777</v>
+        <v>509889</v>
       </c>
       <c r="R103" t="n">
-        <v>7062985</v>
+        <v>7062729</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11887,31 +11916,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11928,7 +11932,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121509950</v>
+        <v>121513009</v>
       </c>
       <c r="B104" t="n">
         <v>57357</v>
@@ -11969,14 +11973,14 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>509687</v>
+        <v>509757</v>
       </c>
       <c r="R104" t="n">
-        <v>7063429</v>
+        <v>7063103</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12035,7 +12039,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121510819</v>
+        <v>121512342</v>
       </c>
       <c r="B105" t="n">
         <v>90746</v>
@@ -12069,16 +12073,21 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>509857</v>
+        <v>509781</v>
       </c>
       <c r="R105" t="n">
-        <v>7063220</v>
+        <v>7063131</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12121,6 +12130,31 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12137,10 +12171,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121510429</v>
+        <v>121513772</v>
       </c>
       <c r="B106" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12153,34 +12187,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>509795</v>
+        <v>509770</v>
       </c>
       <c r="R106" t="n">
-        <v>7063275</v>
+        <v>7063048</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12223,31 +12257,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12264,10 +12273,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121510615</v>
+        <v>121510373</v>
       </c>
       <c r="B107" t="n">
-        <v>79733</v>
+        <v>79697</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12276,38 +12285,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>509826</v>
+        <v>509730</v>
       </c>
       <c r="R107" t="n">
-        <v>7063254</v>
+        <v>7063271</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12350,6 +12364,31 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Salix caprea</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12366,10 +12405,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121512085</v>
+        <v>121511816</v>
       </c>
       <c r="B108" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12382,34 +12421,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>509811</v>
+        <v>509794</v>
       </c>
       <c r="R108" t="n">
-        <v>7063166</v>
+        <v>7063242</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12468,10 +12512,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121511034</v>
+        <v>121513350</v>
       </c>
       <c r="B109" t="n">
-        <v>79732</v>
+        <v>78616</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12480,20 +12524,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12504,19 +12548,19 @@
       <c r="I109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>509872</v>
+        <v>509837</v>
       </c>
       <c r="R109" t="n">
-        <v>7063233</v>
+        <v>7063092</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12567,22 +12611,22 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12600,10 +12644,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121514712</v>
+        <v>121512881</v>
       </c>
       <c r="B110" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12616,39 +12660,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>509680</v>
+        <v>509766</v>
       </c>
       <c r="R110" t="n">
-        <v>7063096</v>
+        <v>7063137</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12681,6 +12720,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12707,10 +12751,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121514198</v>
+        <v>121510352</v>
       </c>
       <c r="B111" t="n">
-        <v>56561</v>
+        <v>90724</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12723,48 +12767,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>509877</v>
+        <v>509738</v>
       </c>
       <c r="R111" t="n">
-        <v>7062713</v>
+        <v>7063269</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12823,10 +12853,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121510935</v>
+        <v>121513795</v>
       </c>
       <c r="B112" t="n">
-        <v>79697</v>
+        <v>90693</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12835,43 +12865,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>509840</v>
+        <v>509761</v>
       </c>
       <c r="R112" t="n">
-        <v>7063219</v>
+        <v>7063058</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12922,22 +12952,22 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -12955,10 +12985,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121510668</v>
+        <v>121513429</v>
       </c>
       <c r="B113" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12971,16 +13001,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12991,22 +13021,22 @@
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>509833</v>
+        <v>509803</v>
       </c>
       <c r="R113" t="n">
-        <v>7063221</v>
+        <v>7063032</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13062,10 +13092,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121511803</v>
+        <v>121513830</v>
       </c>
       <c r="B114" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13078,34 +13108,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>509872</v>
+        <v>509790</v>
       </c>
       <c r="R114" t="n">
-        <v>7063233</v>
+        <v>7063000</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13148,31 +13183,6 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13189,10 +13199,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121511869</v>
+        <v>121510322</v>
       </c>
       <c r="B115" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13205,34 +13215,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>509783</v>
+        <v>509727</v>
       </c>
       <c r="R115" t="n">
-        <v>7063234</v>
+        <v>7063277</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13291,10 +13306,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121509451</v>
+        <v>121513175</v>
       </c>
       <c r="B116" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13307,34 +13322,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>509661</v>
+        <v>509794</v>
       </c>
       <c r="R116" t="n">
-        <v>7063260</v>
+        <v>7063114</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13393,10 +13413,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121512467</v>
+        <v>121514198</v>
       </c>
       <c r="B117" t="n">
-        <v>79697</v>
+        <v>56561</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13409,34 +13429,48 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>509687</v>
+        <v>509877</v>
       </c>
       <c r="R117" t="n">
-        <v>7063193</v>
+        <v>7062713</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13469,11 +13503,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13500,7 +13529,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121510638</v>
+        <v>121512000</v>
       </c>
       <c r="B118" t="n">
         <v>79697</v>
@@ -13536,14 +13565,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>509833</v>
+        <v>509850</v>
       </c>
       <c r="R118" t="n">
-        <v>7063253</v>
+        <v>7063142</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13586,31 +13615,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13627,10 +13631,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121512309</v>
+        <v>121509494</v>
       </c>
       <c r="B119" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13643,39 +13647,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>509781</v>
+        <v>509623</v>
       </c>
       <c r="R119" t="n">
-        <v>7063131</v>
+        <v>7063243</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13736,12 +13735,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13759,10 +13758,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121510833</v>
+        <v>121512199</v>
       </c>
       <c r="B120" t="n">
-        <v>56561</v>
+        <v>82400</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13775,48 +13774,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>509857</v>
+        <v>509781</v>
       </c>
       <c r="R120" t="n">
-        <v>7063220</v>
+        <v>7063145</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13875,7 +13860,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121513830</v>
+        <v>121509950</v>
       </c>
       <c r="B121" t="n">
         <v>57357</v>
@@ -13916,14 +13901,14 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>509790</v>
+        <v>509687</v>
       </c>
       <c r="R121" t="n">
-        <v>7063000</v>
+        <v>7063429</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13982,7 +13967,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121509893</v>
+        <v>121514940</v>
       </c>
       <c r="B122" t="n">
         <v>57357</v>
@@ -14018,7 +14003,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14027,10 +14012,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>509672</v>
+        <v>509622</v>
       </c>
       <c r="R122" t="n">
-        <v>7063416</v>
+        <v>7063172</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14089,10 +14074,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121512199</v>
+        <v>121509893</v>
       </c>
       <c r="B123" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14105,34 +14090,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>509781</v>
+        <v>509672</v>
       </c>
       <c r="R123" t="n">
-        <v>7063145</v>
+        <v>7063416</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14191,10 +14181,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121510201</v>
+        <v>121511869</v>
       </c>
       <c r="B124" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14207,21 +14197,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14231,10 +14221,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>509782</v>
+        <v>509783</v>
       </c>
       <c r="R124" t="n">
-        <v>7063393</v>
+        <v>7063234</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14395,10 +14385,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121513661</v>
+        <v>121509451</v>
       </c>
       <c r="B126" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14411,42 +14401,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>509799</v>
+        <v>509661</v>
       </c>
       <c r="R126" t="n">
-        <v>7063072</v>
+        <v>7063260</v>
       </c>
       <c r="S126" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14502,10 +14487,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121513870</v>
+        <v>121511034</v>
       </c>
       <c r="B127" t="n">
-        <v>56561</v>
+        <v>79732</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14514,52 +14499,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>509786</v>
+        <v>509872</v>
       </c>
       <c r="R127" t="n">
-        <v>7062954</v>
+        <v>7063233</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14602,6 +14578,31 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
@@ -14618,10 +14619,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121513205</v>
+        <v>121512467</v>
       </c>
       <c r="B128" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14634,39 +14635,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>509802</v>
+        <v>509687</v>
       </c>
       <c r="R128" t="n">
-        <v>7063094</v>
+        <v>7063193</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14699,6 +14695,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14725,10 +14726,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121512881</v>
+        <v>121513877</v>
       </c>
       <c r="B129" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14741,34 +14742,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>509766</v>
+        <v>509777</v>
       </c>
       <c r="R129" t="n">
-        <v>7063137</v>
+        <v>7062985</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14803,11 +14809,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14816,6 +14817,31 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -14832,10 +14858,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121512000</v>
+        <v>121513947</v>
       </c>
       <c r="B130" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14848,34 +14874,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>509850</v>
+        <v>509796</v>
       </c>
       <c r="R130" t="n">
-        <v>7063142</v>
+        <v>7062825</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14934,10 +14965,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121510607</v>
+        <v>121512479</v>
       </c>
       <c r="B131" t="n">
-        <v>79726</v>
+        <v>82400</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14946,25 +14977,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14974,10 +15005,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>509826</v>
+        <v>509676</v>
       </c>
       <c r="R131" t="n">
-        <v>7063254</v>
+        <v>7063208</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15036,10 +15067,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121509381</v>
+        <v>121512994</v>
       </c>
       <c r="B132" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15052,39 +15083,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>509555</v>
+        <v>509678</v>
       </c>
       <c r="R132" t="n">
-        <v>7063261</v>
+        <v>7063166</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15127,6 +15158,31 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
@@ -15143,10 +15199,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121509655</v>
+        <v>121510016</v>
       </c>
       <c r="B133" t="n">
-        <v>57510</v>
+        <v>82400</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15159,48 +15215,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>509663</v>
+        <v>509723</v>
       </c>
       <c r="R133" t="n">
-        <v>7063347</v>
+        <v>7063385</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15243,11 +15285,6 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -15264,10 +15301,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121513550</v>
+        <v>121510819</v>
       </c>
       <c r="B134" t="n">
-        <v>90724</v>
+        <v>90746</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15280,39 +15317,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>509824</v>
+        <v>509857</v>
       </c>
       <c r="R134" t="n">
-        <v>7063064</v>
+        <v>7063220</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15355,26 +15387,6 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
@@ -15391,7 +15403,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121513429</v>
+        <v>121512309</v>
       </c>
       <c r="B135" t="n">
         <v>57373</v>
@@ -15427,7 +15439,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15436,13 +15448,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>509803</v>
+        <v>509781</v>
       </c>
       <c r="R135" t="n">
-        <v>7063032</v>
+        <v>7063131</v>
       </c>
       <c r="S135" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15482,6 +15494,31 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -15498,10 +15535,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121509587</v>
+        <v>121510687</v>
       </c>
       <c r="B136" t="n">
-        <v>57373</v>
+        <v>90724</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15514,43 +15551,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>509623</v>
+        <v>509845</v>
       </c>
       <c r="R136" t="n">
-        <v>7063364</v>
+        <v>7063217</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15609,7 +15637,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121511810</v>
+        <v>121513119</v>
       </c>
       <c r="B137" t="n">
         <v>57357</v>
@@ -15650,14 +15678,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>509809</v>
+        <v>509745</v>
       </c>
       <c r="R137" t="n">
-        <v>7063240</v>
+        <v>7063108</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15716,7 +15744,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121510322</v>
+        <v>121514245</v>
       </c>
       <c r="B138" t="n">
         <v>57357</v>
@@ -15757,14 +15785,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>509727</v>
+        <v>509882</v>
       </c>
       <c r="R138" t="n">
-        <v>7063277</v>
+        <v>7062753</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15823,7 +15851,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121510877</v>
+        <v>121510668</v>
       </c>
       <c r="B139" t="n">
         <v>57357</v>
@@ -15859,7 +15887,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -15868,10 +15896,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>509859</v>
+        <v>509833</v>
       </c>
       <c r="R139" t="n">
-        <v>7063248</v>
+        <v>7063221</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15930,10 +15958,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121510661</v>
+        <v>121509655</v>
       </c>
       <c r="B140" t="n">
-        <v>90746</v>
+        <v>57510</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15946,34 +15974,48 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>509840</v>
+        <v>509663</v>
       </c>
       <c r="R140" t="n">
-        <v>7063229</v>
+        <v>7063347</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16016,6 +16058,11 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -16032,10 +16079,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121510253</v>
+        <v>121509421</v>
       </c>
       <c r="B141" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16048,21 +16095,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16072,10 +16119,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>509663</v>
+        <v>509608</v>
       </c>
       <c r="R141" t="n">
-        <v>7063347</v>
+        <v>7063256</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16118,31 +16165,6 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -16159,10 +16181,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121512202</v>
+        <v>121513387</v>
       </c>
       <c r="B142" t="n">
-        <v>74722</v>
+        <v>90724</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16175,34 +16197,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>509783</v>
+        <v>509837</v>
       </c>
       <c r="R142" t="n">
-        <v>7063144</v>
+        <v>7063092</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16245,6 +16272,31 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
@@ -16261,7 +16313,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121509799</v>
+        <v>121509381</v>
       </c>
       <c r="B143" t="n">
         <v>57373</v>
@@ -16294,19 +16346,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -16315,10 +16358,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>509638</v>
+        <v>509555</v>
       </c>
       <c r="R143" t="n">
-        <v>7063385</v>
+        <v>7063261</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16377,10 +16420,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121513795</v>
+        <v>121510881</v>
       </c>
       <c r="B144" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16389,43 +16432,43 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>509761</v>
+        <v>509857</v>
       </c>
       <c r="R144" t="n">
-        <v>7063058</v>
+        <v>7063220</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16468,31 +16511,6 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
@@ -16509,10 +16527,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121509895</v>
+        <v>121509418</v>
       </c>
       <c r="B145" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16525,27 +16543,31 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16554,10 +16576,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>509672</v>
+        <v>509603</v>
       </c>
       <c r="R145" t="n">
-        <v>7063419</v>
+        <v>7063266</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16616,10 +16638,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121512620</v>
+        <v>121509983</v>
       </c>
       <c r="B146" t="n">
-        <v>57510</v>
+        <v>82400</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16632,48 +16654,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>509672</v>
+        <v>509716</v>
       </c>
       <c r="R146" t="n">
-        <v>7063185</v>
+        <v>7063402</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16716,11 +16724,6 @@
       </c>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -16737,10 +16740,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121512670</v>
+        <v>121511099</v>
       </c>
       <c r="B147" t="n">
-        <v>90728</v>
+        <v>79698</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16753,34 +16756,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>509744</v>
+        <v>509872</v>
       </c>
       <c r="R147" t="n">
-        <v>7063125</v>
+        <v>7063233</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16815,6 +16818,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
@@ -16823,6 +16831,31 @@
       </c>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -16839,10 +16872,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121510799</v>
+        <v>121512363</v>
       </c>
       <c r="B148" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16855,27 +16888,27 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16884,10 +16917,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>509846</v>
+        <v>509704</v>
       </c>
       <c r="R148" t="n">
-        <v>7063221</v>
+        <v>7063224</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16946,10 +16979,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121512577</v>
+        <v>121510833</v>
       </c>
       <c r="B149" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16962,34 +16995,48 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>509672</v>
+        <v>509857</v>
       </c>
       <c r="R149" t="n">
-        <v>7063185</v>
+        <v>7063220</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17032,31 +17079,6 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -17073,10 +17095,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121514245</v>
+        <v>121509799</v>
       </c>
       <c r="B150" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17089,16 +17111,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -17106,22 +17128,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>509882</v>
+        <v>509638</v>
       </c>
       <c r="R150" t="n">
-        <v>7062753</v>
+        <v>7063385</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17180,10 +17211,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121513175</v>
+        <v>121510607</v>
       </c>
       <c r="B151" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17192,43 +17223,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>509794</v>
+        <v>509826</v>
       </c>
       <c r="R151" t="n">
-        <v>7063114</v>
+        <v>7063254</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17287,10 +17313,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121513063</v>
+        <v>121512782</v>
       </c>
       <c r="B152" t="n">
-        <v>57357</v>
+        <v>74714</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17303,39 +17329,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>509741</v>
+        <v>509731</v>
       </c>
       <c r="R152" t="n">
-        <v>7063089</v>
+        <v>7063132</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17394,10 +17415,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121512290</v>
+        <v>121510877</v>
       </c>
       <c r="B153" t="n">
-        <v>91411</v>
+        <v>57357</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17406,43 +17427,43 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>509781</v>
+        <v>509859</v>
       </c>
       <c r="R153" t="n">
-        <v>7063131</v>
+        <v>7063248</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17485,31 +17506,6 @@
       </c>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -17526,10 +17522,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121510603</v>
+        <v>121512620</v>
       </c>
       <c r="B154" t="n">
-        <v>79698</v>
+        <v>57510</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17542,34 +17538,48 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>509826</v>
+        <v>509672</v>
       </c>
       <c r="R154" t="n">
-        <v>7063254</v>
+        <v>7063185</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17612,6 +17622,11 @@
       </c>
       <c r="AG154" t="b">
         <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
@@ -17628,10 +17643,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121513350</v>
+        <v>121512290</v>
       </c>
       <c r="B155" t="n">
-        <v>78616</v>
+        <v>91411</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17640,31 +17655,31 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17673,10 +17688,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>509837</v>
+        <v>509781</v>
       </c>
       <c r="R155" t="n">
-        <v>7063092</v>
+        <v>7063131</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17737,12 +17752,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -17760,10 +17775,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121511059</v>
+        <v>121510603</v>
       </c>
       <c r="B156" t="n">
-        <v>79733</v>
+        <v>79698</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17772,43 +17787,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>509872</v>
+        <v>509826</v>
       </c>
       <c r="R156" t="n">
-        <v>7063233</v>
+        <v>7063254</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17851,31 +17861,6 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
@@ -17892,10 +17877,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121512903</v>
+        <v>121512577</v>
       </c>
       <c r="B157" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17908,39 +17893,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>509758</v>
+        <v>509672</v>
       </c>
       <c r="R157" t="n">
-        <v>7063118</v>
+        <v>7063185</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17983,6 +17963,31 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
@@ -17999,10 +18004,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121510881</v>
+        <v>121510615</v>
       </c>
       <c r="B158" t="n">
-        <v>57357</v>
+        <v>79733</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18011,43 +18016,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>509857</v>
+        <v>509826</v>
       </c>
       <c r="R158" t="n">
-        <v>7063220</v>
+        <v>7063254</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18106,10 +18106,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121509417</v>
+        <v>121510799</v>
       </c>
       <c r="B159" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18122,27 +18122,27 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -18151,10 +18151,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>509606</v>
+        <v>509846</v>
       </c>
       <c r="R159" t="n">
-        <v>7063266</v>
+        <v>7063221</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18213,10 +18213,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121512994</v>
+        <v>121514712</v>
       </c>
       <c r="B160" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18229,27 +18229,27 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -18258,10 +18258,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>509678</v>
+        <v>509680</v>
       </c>
       <c r="R160" t="n">
-        <v>7063166</v>
+        <v>7063096</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18304,31 +18304,6 @@
       </c>
       <c r="AG160" t="b">
         <v>0</v>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
@@ -18345,10 +18320,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121509983</v>
+        <v>121513661</v>
       </c>
       <c r="B161" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18361,37 +18336,42 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>509716</v>
+        <v>509799</v>
       </c>
       <c r="R161" t="n">
-        <v>7063402</v>
+        <v>7063072</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18447,10 +18427,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121511816</v>
+        <v>121513550</v>
       </c>
       <c r="B162" t="n">
-        <v>57357</v>
+        <v>90724</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18463,39 +18443,39 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>509794</v>
+        <v>509824</v>
       </c>
       <c r="R162" t="n">
-        <v>7063242</v>
+        <v>7063064</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18538,6 +18518,26 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -18554,7 +18554,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121514280</v>
+        <v>121513063</v>
       </c>
       <c r="B163" t="n">
         <v>57357</v>
@@ -18590,7 +18590,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -18599,10 +18599,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>509889</v>
+        <v>509741</v>
       </c>
       <c r="R163" t="n">
-        <v>7062729</v>
+        <v>7063089</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18661,10 +18661,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121513768</v>
+        <v>121536121</v>
       </c>
       <c r="B164" t="n">
-        <v>90675</v>
+        <v>79732</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18673,41 +18673,45 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>112</v>
+        <v>6463</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>509770</v>
+        <v>509840</v>
       </c>
       <c r="R164" t="n">
-        <v>7063048</v>
+        <v>7063219</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18742,6 +18746,11 @@
           <t>2024-12-08</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>På en gammal skadad sälg</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -18759,22 +18768,22 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -18792,10 +18801,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121512270</v>
+        <v>121509473</v>
       </c>
       <c r="B165" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18808,41 +18817,39 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>teleomorf</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>509872</v>
+        <v>509623</v>
       </c>
       <c r="R165" t="n">
-        <v>7063233</v>
+        <v>7063243</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18883,7 +18890,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18904,12 +18910,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -18927,7 +18933,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121509473</v>
+        <v>121536426</v>
       </c>
       <c r="B166" t="n">
         <v>90728</v>
@@ -18961,21 +18967,23 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>teleomorf</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>509623</v>
+        <v>510009</v>
       </c>
       <c r="R166" t="n">
-        <v>7063243</v>
+        <v>7063068</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19002,12 +19010,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19016,6 +19024,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -19199,10 +19208,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121536426</v>
+        <v>121513396</v>
       </c>
       <c r="B168" t="n">
-        <v>90728</v>
+        <v>88046</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19215,21 +19224,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19242,14 +19251,14 @@
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>510009</v>
+        <v>509841</v>
       </c>
       <c r="R168" t="n">
-        <v>7063068</v>
+        <v>7063053</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19276,12 +19285,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19311,12 +19320,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -19334,10 +19343,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121510598</v>
+        <v>121501176</v>
       </c>
       <c r="B169" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19350,41 +19359,41 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>509826</v>
+        <v>509999</v>
       </c>
       <c r="R169" t="n">
-        <v>7063254</v>
+        <v>7062971</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19411,12 +19420,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19436,27 +19445,22 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL169" t="inlineStr">
-        <is>
-          <t>En gammal skadad men levande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal skadad men levande sälg.</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
@@ -19474,10 +19478,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121536121</v>
+        <v>121513768</v>
       </c>
       <c r="B170" t="n">
-        <v>79732</v>
+        <v>90675</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19486,45 +19490,41 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6463</v>
+        <v>112</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>509840</v>
+        <v>509770</v>
       </c>
       <c r="R170" t="n">
-        <v>7063219</v>
+        <v>7063048</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19559,11 +19559,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>På en gammal skadad sälg</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -19581,22 +19576,22 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -19614,10 +19609,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121512242</v>
+        <v>121512270</v>
       </c>
       <c r="B171" t="n">
-        <v>57510</v>
+        <v>90746</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19630,53 +19625,44 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Sörpkaret, Nyland, Gåxsjö, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>509733</v>
+        <v>509872</v>
       </c>
       <c r="R171" t="n">
-        <v>7063175</v>
+        <v>7063233</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19714,12 +19700,33 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -19737,10 +19744,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121509637</v>
+        <v>121511009</v>
       </c>
       <c r="B172" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19753,46 +19760,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>509663</v>
+        <v>509876</v>
       </c>
       <c r="R172" t="n">
-        <v>7063347</v>
+        <v>7063213</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19829,7 +19824,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack.</t>
+          <t>På en grovbarkad sälglåga.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19848,22 +19843,22 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -20018,10 +20013,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121511009</v>
+        <v>121512242</v>
       </c>
       <c r="B174" t="n">
-        <v>79697</v>
+        <v>57510</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -20034,37 +20029,53 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
+          <t>Sörpkaret, Nyland, Gåxsjö, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>509876</v>
+        <v>509733</v>
       </c>
       <c r="R174" t="n">
-        <v>7063213</v>
+        <v>7063175</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20096,11 +20107,6 @@
           <t>2024-12-08</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -20113,26 +20119,6 @@
       <c r="AH174" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
@@ -20260,10 +20246,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121501176</v>
+        <v>121510598</v>
       </c>
       <c r="B176" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20276,41 +20262,41 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>509999</v>
+        <v>509826</v>
       </c>
       <c r="R176" t="n">
-        <v>7062971</v>
+        <v>7063254</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20337,12 +20323,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20362,22 +20348,27 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr">
+        <is>
+          <t>En gammal skadad men levande sälg.</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal skadad men levande sälg.</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -20395,10 +20386,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121513396</v>
+        <v>121537514</v>
       </c>
       <c r="B177" t="n">
-        <v>88046</v>
+        <v>91072</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20407,34 +20398,30 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>510</v>
+        <v>2062</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
@@ -20442,10 +20429,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>509841</v>
+        <v>509999</v>
       </c>
       <c r="R177" t="n">
-        <v>7063053</v>
+        <v>7062971</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20472,12 +20459,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20497,22 +20484,22 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -20530,10 +20517,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121537514</v>
+        <v>121509637</v>
       </c>
       <c r="B178" t="n">
-        <v>91072</v>
+        <v>57357</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20542,41 +20529,50 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Stor-Älgflotjärnen, Stor-Älgflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>509999</v>
+        <v>509663</v>
       </c>
       <c r="R178" t="n">
-        <v>7062971</v>
+        <v>7063347</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20603,12 +20599,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20617,7 +20618,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -20628,22 +20628,22 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Phellinidium ferrugineofuscum</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -20661,10 +20661,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121502652</v>
+        <v>121541263</v>
       </c>
       <c r="B179" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20677,37 +20677,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>510074</v>
+        <v>509813</v>
       </c>
       <c r="R179" t="n">
-        <v>7063170</v>
+        <v>7063049</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20742,13 +20747,17 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -20769,12 +20778,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -20792,10 +20801,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121541339</v>
+        <v>121541649</v>
       </c>
       <c r="B180" t="n">
-        <v>79601</v>
+        <v>82400</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20804,25 +20813,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20835,10 +20844,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>510072</v>
+        <v>510075</v>
       </c>
       <c r="R180" t="n">
-        <v>7063162</v>
+        <v>7063176</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20873,11 +20882,6 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>På en grov asp med brösthöjdsdiameter på 84,5 cm.</t>
-        </is>
-      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
@@ -20887,31 +20891,6 @@
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
-        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
@@ -20928,10 +20907,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121541649</v>
+        <v>121502652</v>
       </c>
       <c r="B181" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20944,21 +20923,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20967,14 +20946,14 @@
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>510075</v>
+        <v>510074</v>
       </c>
       <c r="R181" t="n">
-        <v>7063176</v>
+        <v>7063170</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21018,6 +20997,31 @@
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
@@ -21034,10 +21038,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121541263</v>
+        <v>121541339</v>
       </c>
       <c r="B182" t="n">
-        <v>57357</v>
+        <v>79601</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21046,35 +21050,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
@@ -21082,10 +21081,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>509813</v>
+        <v>510072</v>
       </c>
       <c r="R182" t="n">
-        <v>7063049</v>
+        <v>7063162</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21122,7 +21121,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>På en grov asp med brösthöjdsdiameter på 84,5 cm.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21131,6 +21130,7 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
@@ -21141,22 +21141,22 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -20907,10 +20907,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121502652</v>
+        <v>121541339</v>
       </c>
       <c r="B181" t="n">
-        <v>78616</v>
+        <v>79601</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20919,25 +20919,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20946,14 +20946,14 @@
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>510074</v>
+        <v>510072</v>
       </c>
       <c r="R181" t="n">
-        <v>7063170</v>
+        <v>7063162</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20988,6 +20988,11 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>På en grov asp med brösthöjdsdiameter på 84,5 cm.</t>
+        </is>
+      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
@@ -21005,22 +21010,22 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -21038,10 +21043,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121541339</v>
+        <v>121502652</v>
       </c>
       <c r="B182" t="n">
-        <v>79601</v>
+        <v>78616</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21050,25 +21055,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21077,14 +21082,14 @@
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>510072</v>
+        <v>510074</v>
       </c>
       <c r="R182" t="n">
-        <v>7063162</v>
+        <v>7063170</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21119,11 +21124,6 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>På en grov asp med brösthöjdsdiameter på 84,5 cm.</t>
-        </is>
-      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
@@ -21141,22 +21141,22 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -20907,10 +20907,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121541339</v>
+        <v>121540413</v>
       </c>
       <c r="B181" t="n">
-        <v>79601</v>
+        <v>57357</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20919,41 +20919,46 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Nyland, Gåxsjö, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>510072</v>
+        <v>510014</v>
       </c>
       <c r="R181" t="n">
-        <v>7063162</v>
+        <v>7063010</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20988,45 +20993,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>På en grov asp med brösthöjdsdiameter på 84,5 cm.</t>
-        </is>
-      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
@@ -21043,10 +21017,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121502652</v>
+        <v>121541339</v>
       </c>
       <c r="B182" t="n">
-        <v>78616</v>
+        <v>79601</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21055,25 +21029,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21082,14 +21056,14 @@
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Sörpkaret, Sörpkaret, Jmt</t>
+          <t>Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>510074</v>
+        <v>510072</v>
       </c>
       <c r="R182" t="n">
-        <v>7063170</v>
+        <v>7063162</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21124,6 +21098,11 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>På en grov asp med brösthöjdsdiameter på 84,5 cm.</t>
+        </is>
+      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
@@ -21141,22 +21120,22 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -21174,10 +21153,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121540413</v>
+        <v>121502652</v>
       </c>
       <c r="B183" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21190,42 +21169,37 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Sörpkaret, Nyland, Gåxsjö, Jmt</t>
+          <t>Sörpkaret, Sörpkaret, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>510014</v>
+        <v>510074</v>
       </c>
       <c r="R183" t="n">
-        <v>7063010</v>
+        <v>7063170</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21266,8 +21240,34 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -21287,7 +21287,7 @@
         <v>121499500</v>
       </c>
       <c r="B184" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -9225,7 +9225,7 @@
         <v>121509673</v>
       </c>
       <c r="B80" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -9240,11 +9240,6 @@
       <c r="E80" t="n">
         <v>100109</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -9225,7 +9225,7 @@
         <v>121509673</v>
       </c>
       <c r="B80" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9239,6 +9239,11 @@
       </c>
       <c r="E80" t="n">
         <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>

--- a/artfynd/A 51461-2024 artfynd.xlsx
+++ b/artfynd/A 51461-2024 artfynd.xlsx
@@ -9225,7 +9225,7 @@
         <v>121509673</v>
       </c>
       <c r="B80" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
